--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/09-caixa-do-escritorio.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/09-caixa-do-escritorio.xlsx
@@ -248,7 +248,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1060,7 +1062,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!B4&amp;" · Caixa do escritório · "&amp;Config!B6&amp;" de "&amp;Config!B5</f>
         <v/>
@@ -3245,7 +3247,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="43">
+  <mergeCells count="44">
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F9:I9"/>
@@ -3285,6 +3287,7 @@
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="F8:I8"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="F23:I23"/>
@@ -3328,7 +3331,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações</t>
@@ -3884,8 +3887,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -3918,7 +3922,7 @@
     <col width="7" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Lançamentos</t>
@@ -20720,8 +20724,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:K604"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:K604">
     <cfRule type="expression" priority="1" dxfId="2">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/09-caixa-do-escritorio.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/09-caixa-do-escritorio.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -268,16 +269,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -287,7 +288,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -295,7 +296,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,13 +311,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -856,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1017,17 +1018,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1136,7 +1149,7 @@
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="18">
         <f>SUMIFS(Lançamentos!$G$5:$G$604,Lançamentos!$B$5:$B$604,"Entrada",Lançamentos!$I$5:$I$604,"Não")</f>
-        <v>27330</v>
+        <v>25930</v>
       </c>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="18">
@@ -2267,7 +2280,7 @@
       </c>
       <c r="E50" s="24">
         <f>IF(Config!$J$10="","",SUMIFS(Lançamentos!$G$5:$G$604,Lançamentos!$B$5:$B$604,"Entrada",Lançamentos!$I$5:$I$604,"Não",Lançamentos!$D$5:$D$604,Config!$J$10))</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="F50" s="24">
         <f>IF(Config!$J$10="","",SUMIFS(Lançamentos!$G$5:$G$604,Lançamentos!$B$5:$B$604,"Saída",Lançamentos!$I$5:$I$604,"Sim",Lançamentos!$D$5:$D$604,Config!$J$10,Lançamentos!$K$5:$K$604,Config!$B$5))</f>
@@ -2914,7 +2927,7 @@
       </c>
       <c r="E75" s="28">
         <f>SUM(E45:E74)</f>
-        <v>27330</v>
+        <v>25930</v>
       </c>
       <c r="F75" s="28">
         <f>SUM(F45:F74)</f>
@@ -3527,9 +3540,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B9" s="37">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B9" s="37" t="n">
+        <v>46279</v>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
@@ -5702,44 +5714,36 @@
     </row>
     <row r="41">
       <c r="A41" s="38" t="n">
-        <v>46066</v>
+        <v>46068</v>
       </c>
       <c r="B41" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D41" s="31" t="inlineStr">
-        <is>
-          <t>Fernanda Castro</t>
-        </is>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>5211189-81.2025.8.26.0412</t>
-        </is>
-      </c>
+          <t>Anuidades OAB e cursos</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr"/>
+      <c r="E41" s="31" t="inlineStr"/>
       <c r="F41" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 4 (vencida)</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G41" s="36" t="n">
-        <v>1400</v>
+        <v>250</v>
       </c>
       <c r="H41" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I41" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J41" s="35">
@@ -5753,31 +5757,39 @@
     </row>
     <row r="42">
       <c r="A42" s="38" t="n">
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="B42" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C42" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
-        </is>
-      </c>
-      <c r="D42" s="31" t="inlineStr"/>
-      <c r="E42" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>Padaria do Sol Ltda</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>4766902-26.2025.8.26.0051</t>
+        </is>
+      </c>
       <c r="F42" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G42" s="36" t="n">
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="H42" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I42" s="32" t="inlineStr">
@@ -5800,35 +5812,27 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D43" s="31" t="inlineStr">
-        <is>
-          <t>Padaria do Sol Ltda</t>
-        </is>
-      </c>
-      <c r="E43" s="31" t="inlineStr">
-        <is>
-          <t>4766902-26.2025.8.26.0051</t>
-        </is>
-      </c>
+          <t>Deslocamento e viagens</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr"/>
+      <c r="E43" s="31" t="inlineStr"/>
       <c r="F43" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Combustível e estacionamento (audiências)</t>
         </is>
       </c>
       <c r="G43" s="36" t="n">
-        <v>2250</v>
+        <v>240</v>
       </c>
       <c r="H43" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I43" s="32" t="inlineStr">
@@ -5847,7 +5851,7 @@
     </row>
     <row r="44">
       <c r="A44" s="38" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B44" s="32" t="inlineStr">
         <is>
@@ -5856,18 +5860,18 @@
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>Deslocamento e viagens</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="D44" s="31" t="inlineStr"/>
       <c r="E44" s="31" t="inlineStr"/>
       <c r="F44" s="31" t="inlineStr">
         <is>
-          <t>Combustível e estacionamento (audiências)</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G44" s="36" t="n">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="H44" s="32" t="inlineStr">
         <is>
@@ -5890,31 +5894,39 @@
     </row>
     <row r="45">
       <c r="A45" s="38" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B45" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D45" s="31" t="inlineStr"/>
-      <c r="E45" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>Bistrô 42</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>8056747-83.2026.8.26.0561</t>
+        </is>
+      </c>
       <c r="F45" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G45" s="36" t="n">
-        <v>380</v>
+        <v>2100</v>
       </c>
       <c r="H45" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I45" s="32" t="inlineStr">
@@ -5937,35 +5949,27 @@
       </c>
       <c r="B46" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D46" s="31" t="inlineStr">
-        <is>
-          <t>Bistrô 42</t>
-        </is>
-      </c>
-      <c r="E46" s="31" t="inlineStr">
-        <is>
-          <t>8056747-83.2026.8.26.0561</t>
-        </is>
-      </c>
+          <t>Impostos e taxas</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr"/>
+      <c r="E46" s="31" t="inlineStr"/>
       <c r="F46" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G46" s="36" t="n">
-        <v>2100</v>
+        <v>1684</v>
       </c>
       <c r="H46" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I46" s="32" t="inlineStr">
@@ -5993,22 +5997,22 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D47" s="31" t="inlineStr"/>
       <c r="E47" s="31" t="inlineStr"/>
       <c r="F47" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G47" s="36" t="n">
-        <v>1684</v>
+        <v>400</v>
       </c>
       <c r="H47" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I47" s="32" t="inlineStr">
@@ -6027,7 +6031,7 @@
     </row>
     <row r="48">
       <c r="A48" s="38" t="n">
-        <v>46073</v>
+        <v>46081</v>
       </c>
       <c r="B48" s="32" t="inlineStr">
         <is>
@@ -6036,22 +6040,22 @@
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Pró-labore dos sócios</t>
         </is>
       </c>
       <c r="D48" s="31" t="inlineStr"/>
       <c r="E48" s="31" t="inlineStr"/>
       <c r="F48" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G48" s="36" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I48" s="32" t="inlineStr">
@@ -6086,7 +6090,7 @@
       <c r="E49" s="31" t="inlineStr"/>
       <c r="F49" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G49" s="36" t="n">
@@ -6113,31 +6117,39 @@
     </row>
     <row r="50">
       <c r="A50" s="38" t="n">
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="B50" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D50" s="31" t="inlineStr"/>
-      <c r="E50" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>3363714-92.2025.8.26.0592</t>
+        </is>
+      </c>
       <c r="F50" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G50" s="36" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I50" s="32" t="inlineStr">
@@ -6147,7 +6159,7 @@
       </c>
       <c r="J50" s="35">
         <f>IF(A50="","",MONTH(A50))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="35">
         <f>IF(A50="","",YEAR(A50))</f>
@@ -6156,39 +6168,39 @@
     </row>
     <row r="51">
       <c r="A51" s="38" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B51" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Custas e despesas de processo</t>
         </is>
       </c>
       <c r="D51" s="31" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="E51" s="31" t="inlineStr">
         <is>
-          <t>3363714-92.2025.8.26.0592</t>
+          <t>9225646-96.2025.8.26.0322</t>
         </is>
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Diligência de oficial de justiça</t>
         </is>
       </c>
       <c r="G51" s="36" t="n">
-        <v>2000</v>
+        <v>130</v>
       </c>
       <c r="H51" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I51" s="32" t="inlineStr">
@@ -6207,7 +6219,7 @@
     </row>
     <row r="52">
       <c r="A52" s="38" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B52" s="32" t="inlineStr">
         <is>
@@ -6216,26 +6228,18 @@
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
-        </is>
-      </c>
-      <c r="D52" s="31" t="inlineStr">
-        <is>
-          <t>Transportadora Rota Sul</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>9225646-96.2025.8.26.0322</t>
-        </is>
-      </c>
+          <t>Aluguel e condomínio</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="inlineStr"/>
+      <c r="E52" s="31" t="inlineStr"/>
       <c r="F52" s="31" t="inlineStr">
         <is>
-          <t>Diligência de oficial de justiça</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G52" s="36" t="n">
-        <v>130</v>
+        <v>2800</v>
       </c>
       <c r="H52" s="32" t="inlineStr">
         <is>
@@ -6267,22 +6271,22 @@
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
+          <t>Estagiária (bolsa)</t>
         </is>
       </c>
       <c r="D53" s="31" t="inlineStr"/>
       <c r="E53" s="31" t="inlineStr"/>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G53" s="36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H53" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I53" s="32" t="inlineStr">
@@ -6301,7 +6305,7 @@
     </row>
     <row r="54">
       <c r="A54" s="38" t="n">
-        <v>46086</v>
+        <v>46089</v>
       </c>
       <c r="B54" s="32" t="inlineStr">
         <is>
@@ -6310,18 +6314,18 @@
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="D54" s="31" t="inlineStr"/>
       <c r="E54" s="31" t="inlineStr"/>
       <c r="F54" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G54" s="36" t="n">
-        <v>1400</v>
+        <v>450</v>
       </c>
       <c r="H54" s="32" t="inlineStr">
         <is>
@@ -6344,31 +6348,39 @@
     </row>
     <row r="55">
       <c r="A55" s="38" t="n">
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="B55" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
-        </is>
-      </c>
-      <c r="D55" s="31" t="inlineStr"/>
-      <c r="E55" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D55" s="31" t="inlineStr">
+        <is>
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>5025425-10.2025.8.26.0629</t>
+        </is>
+      </c>
       <c r="F55" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G55" s="36" t="n">
-        <v>450</v>
+        <v>3000</v>
       </c>
       <c r="H55" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I55" s="32" t="inlineStr">
@@ -6396,30 +6408,30 @@
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Reembolso de custas</t>
         </is>
       </c>
       <c r="D56" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Construtora Horizonte</t>
         </is>
       </c>
       <c r="E56" s="31" t="inlineStr">
         <is>
-          <t>5025425-10.2025.8.26.0629</t>
+          <t>9778116-95.2025.8.26.0106</t>
         </is>
       </c>
       <c r="F56" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Reembolso das custas periciais</t>
         </is>
       </c>
       <c r="G56" s="36" t="n">
-        <v>3000</v>
+        <v>780</v>
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I56" s="32" t="inlineStr">
@@ -6438,7 +6450,7 @@
     </row>
     <row r="57">
       <c r="A57" s="38" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B57" s="32" t="inlineStr">
         <is>
@@ -6447,30 +6459,30 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>Reembolso de custas</t>
+          <t>Consultoria e pareceres</t>
         </is>
       </c>
       <c r="D57" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="E57" s="31" t="inlineStr">
         <is>
-          <t>9778116-95.2025.8.26.0106</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="F57" s="31" t="inlineStr">
         <is>
-          <t>Reembolso das custas periciais</t>
+          <t>Fatura de horas · 4</t>
         </is>
       </c>
       <c r="G57" s="36" t="n">
-        <v>780</v>
+        <v>2340</v>
       </c>
       <c r="H57" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I57" s="32" t="inlineStr">
@@ -6498,26 +6510,26 @@
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D58" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E58" s="31" t="inlineStr">
         <is>
-          <t>CONS-2025-05</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F58" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 4</t>
+          <t>Fatura de horas · 3</t>
         </is>
       </c>
       <c r="G58" s="36" t="n">
-        <v>2340</v>
+        <v>2520</v>
       </c>
       <c r="H58" s="32" t="inlineStr">
         <is>
@@ -6544,31 +6556,23 @@
       </c>
       <c r="B59" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
-        </is>
-      </c>
-      <c r="D59" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>9362688-24.2025.8.26.0436</t>
-        </is>
-      </c>
+          <t>Contador</t>
+        </is>
+      </c>
+      <c r="D59" s="31" t="inlineStr"/>
+      <c r="E59" s="31" t="inlineStr"/>
       <c r="F59" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 3</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G59" s="36" t="n">
-        <v>2520</v>
+        <v>600</v>
       </c>
       <c r="H59" s="32" t="inlineStr">
         <is>
@@ -6591,7 +6595,7 @@
     </row>
     <row r="60">
       <c r="A60" s="38" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B60" s="32" t="inlineStr">
         <is>
@@ -6600,22 +6604,22 @@
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
+          <t>Outras saídas</t>
         </is>
       </c>
       <c r="D60" s="31" t="inlineStr"/>
       <c r="E60" s="31" t="inlineStr"/>
       <c r="F60" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Despesa pessoal · Rafael Lima · combustível particular (a acertar)</t>
         </is>
       </c>
       <c r="G60" s="36" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H60" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I60" s="32" t="inlineStr">
@@ -6634,31 +6638,39 @@
     </row>
     <row r="61">
       <c r="A61" s="38" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>Outras saídas</t>
-        </is>
-      </c>
-      <c r="D61" s="31" t="inlineStr"/>
-      <c r="E61" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D61" s="31" t="inlineStr">
+        <is>
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>8663770-96.2025.8.26.0481</t>
+        </is>
+      </c>
       <c r="F61" s="31" t="inlineStr">
         <is>
-          <t>Despesa pessoal · Rafael Lima · combustível particular (a acertar)</t>
+          <t>Honorários · parcela 10</t>
         </is>
       </c>
       <c r="G61" s="36" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="H61" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I61" s="32" t="inlineStr">
@@ -6681,35 +6693,27 @@
       </c>
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D62" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E62" s="31" t="inlineStr">
-        <is>
-          <t>8663770-96.2025.8.26.0481</t>
-        </is>
-      </c>
+          <t>Telefone e internet</t>
+        </is>
+      </c>
+      <c r="D62" s="31" t="inlineStr"/>
+      <c r="E62" s="31" t="inlineStr"/>
       <c r="F62" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 10</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G62" s="36" t="n">
-        <v>800</v>
+        <v>220</v>
       </c>
       <c r="H62" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I62" s="32" t="inlineStr">
@@ -6728,7 +6732,7 @@
     </row>
     <row r="63">
       <c r="A63" s="38" t="n">
-        <v>46093</v>
+        <v>46096</v>
       </c>
       <c r="B63" s="32" t="inlineStr">
         <is>
@@ -6737,22 +6741,22 @@
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="D63" s="31" t="inlineStr"/>
       <c r="E63" s="31" t="inlineStr"/>
       <c r="F63" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G63" s="36" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="H63" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr">
@@ -6771,31 +6775,39 @@
     </row>
     <row r="64">
       <c r="A64" s="38" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B64" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C64" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
-        </is>
-      </c>
-      <c r="D64" s="31" t="inlineStr"/>
-      <c r="E64" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D64" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Nunes</t>
+        </is>
+      </c>
+      <c r="E64" s="31" t="inlineStr">
+        <is>
+          <t>8045862-82.2026.8.26.0491</t>
+        </is>
+      </c>
       <c r="F64" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G64" s="36" t="n">
-        <v>250</v>
+        <v>1800</v>
       </c>
       <c r="H64" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I64" s="32" t="inlineStr">
@@ -6818,35 +6830,27 @@
       </c>
       <c r="B65" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D65" s="31" t="inlineStr">
-        <is>
-          <t>Carlos Eduardo Nunes</t>
-        </is>
-      </c>
-      <c r="E65" s="31" t="inlineStr">
-        <is>
-          <t>8045862-82.2026.8.26.0491</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="inlineStr"/>
+      <c r="E65" s="31" t="inlineStr"/>
       <c r="F65" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Retirada extra · Rafael Lima · adiantamento para viagem</t>
         </is>
       </c>
       <c r="G65" s="36" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="H65" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr">
@@ -6865,31 +6869,39 @@
     </row>
     <row r="66">
       <c r="A66" s="38" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B66" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D66" s="31" t="inlineStr"/>
-      <c r="E66" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D66" s="31" t="inlineStr">
+        <is>
+          <t>Padaria do Sol Ltda</t>
+        </is>
+      </c>
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>4766902-26.2025.8.26.0051</t>
+        </is>
+      </c>
       <c r="F66" s="31" t="inlineStr">
         <is>
-          <t>Retirada extra · Rafael Lima · adiantamento para viagem</t>
+          <t>Honorários · parcela 4</t>
         </is>
       </c>
       <c r="G66" s="36" t="n">
-        <v>1500</v>
+        <v>2250</v>
       </c>
       <c r="H66" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I66" s="32" t="inlineStr">
@@ -6908,7 +6920,7 @@
     </row>
     <row r="67">
       <c r="A67" s="38" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B67" s="32" t="inlineStr">
         <is>
@@ -6922,30 +6934,30 @@
       </c>
       <c r="D67" s="31" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="E67" s="31" t="inlineStr">
         <is>
-          <t>4766902-26.2025.8.26.0051</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="F67" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 4</t>
+          <t>Honorários · parcela 2 (vencida)</t>
         </is>
       </c>
       <c r="G67" s="36" t="n">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="H67" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I67" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J67" s="35">
@@ -6963,40 +6975,32 @@
       </c>
       <c r="B68" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C68" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D68" s="31" t="inlineStr">
-        <is>
-          <t>Bistrô 42</t>
-        </is>
-      </c>
-      <c r="E68" s="31" t="inlineStr">
-        <is>
-          <t>8056747-83.2026.8.26.0561</t>
-        </is>
-      </c>
+          <t>Material, correio e outros</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="inlineStr"/>
+      <c r="E68" s="31" t="inlineStr"/>
       <c r="F68" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2 (vencida)</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G68" s="36" t="n">
-        <v>2100</v>
+        <v>380</v>
       </c>
       <c r="H68" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J68" s="35">
@@ -7010,31 +7014,39 @@
     </row>
     <row r="69">
       <c r="A69" s="38" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B69" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D69" s="31" t="inlineStr"/>
-      <c r="E69" s="31" t="inlineStr"/>
+          <t>Honorários de êxito</t>
+        </is>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>Ana Beatriz Moreira</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>9420478-99.2025.8.26.0491</t>
+        </is>
+      </c>
       <c r="F69" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários de êxito (fim do caso)</t>
         </is>
       </c>
       <c r="G69" s="36" t="n">
-        <v>380</v>
+        <v>5500</v>
       </c>
       <c r="H69" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr">
@@ -7062,26 +7074,26 @@
       </c>
       <c r="C70" s="31" t="inlineStr">
         <is>
-          <t>Honorários de êxito</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D70" s="31" t="inlineStr">
         <is>
-          <t>Ana Beatriz Moreira</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="E70" s="31" t="inlineStr">
         <is>
-          <t>9420478-99.2025.8.26.0491</t>
+          <t>9225646-96.2025.8.26.0322</t>
         </is>
       </c>
       <c r="F70" s="31" t="inlineStr">
         <is>
-          <t>Honorários de êxito (fim do caso)</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G70" s="36" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="H70" s="32" t="inlineStr">
         <is>
@@ -7108,35 +7120,27 @@
       </c>
       <c r="B71" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>Transportadora Rota Sul</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>9225646-96.2025.8.26.0322</t>
-        </is>
-      </c>
+          <t>Impostos e taxas</t>
+        </is>
+      </c>
+      <c r="D71" s="31" t="inlineStr"/>
+      <c r="E71" s="31" t="inlineStr"/>
       <c r="F71" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G71" s="36" t="n">
-        <v>2000</v>
+        <v>1846</v>
       </c>
       <c r="H71" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr">
@@ -7164,22 +7168,22 @@
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D72" s="31" t="inlineStr"/>
       <c r="E72" s="31" t="inlineStr"/>
       <c r="F72" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G72" s="36" t="n">
-        <v>1846</v>
+        <v>400</v>
       </c>
       <c r="H72" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr">
@@ -7198,31 +7202,39 @@
     </row>
     <row r="73">
       <c r="A73" s="38" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B73" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="inlineStr"/>
-      <c r="E73" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>6832730-55.2026.8.26.0386</t>
+        </is>
+      </c>
       <c r="F73" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G73" s="36" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="H73" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr">
@@ -7255,21 +7267,21 @@
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="E74" s="31" t="inlineStr">
         <is>
-          <t>6832730-55.2026.8.26.0386</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="F74" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Honorários · parcela 4</t>
         </is>
       </c>
       <c r="G74" s="36" t="n">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="H74" s="32" t="inlineStr">
         <is>
@@ -7292,39 +7304,31 @@
     </row>
     <row r="75">
       <c r="A75" s="38" t="n">
-        <v>46104</v>
+        <v>46109</v>
       </c>
       <c r="B75" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>3363714-92.2025.8.26.0592</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="inlineStr"/>
+      <c r="E75" s="31" t="inlineStr"/>
       <c r="F75" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 4</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G75" s="36" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H75" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr">
@@ -7359,7 +7363,7 @@
       <c r="E76" s="31" t="inlineStr"/>
       <c r="F76" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G76" s="36" t="n">
@@ -7386,7 +7390,7 @@
     </row>
     <row r="77">
       <c r="A77" s="38" t="n">
-        <v>46109</v>
+        <v>46117</v>
       </c>
       <c r="B77" s="32" t="inlineStr">
         <is>
@@ -7395,22 +7399,22 @@
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
+          <t>Aluguel e condomínio</t>
         </is>
       </c>
       <c r="D77" s="31" t="inlineStr"/>
       <c r="E77" s="31" t="inlineStr"/>
       <c r="F77" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G77" s="36" t="n">
-        <v>6000</v>
+        <v>2800</v>
       </c>
       <c r="H77" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr">
@@ -7420,7 +7424,7 @@
       </c>
       <c r="J77" s="35">
         <f>IF(A77="","",MONTH(A77))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77" s="35">
         <f>IF(A77="","",YEAR(A77))</f>
@@ -7438,22 +7442,22 @@
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
+          <t>Estagiária (bolsa)</t>
         </is>
       </c>
       <c r="D78" s="31" t="inlineStr"/>
       <c r="E78" s="31" t="inlineStr"/>
       <c r="F78" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G78" s="36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H78" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr">
@@ -7472,31 +7476,39 @@
     </row>
     <row r="79">
       <c r="A79" s="38" t="n">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="B79" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="inlineStr"/>
-      <c r="E79" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>Transportadora Rota Sul</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>9225646-96.2025.8.26.0322</t>
+        </is>
+      </c>
       <c r="F79" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Honorários · parcela 4</t>
         </is>
       </c>
       <c r="G79" s="36" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H79" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr">
@@ -7519,35 +7531,27 @@
       </c>
       <c r="B80" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>Transportadora Rota Sul</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>9225646-96.2025.8.26.0322</t>
-        </is>
-      </c>
+          <t>Sistemas e assinaturas</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr"/>
+      <c r="E80" s="31" t="inlineStr"/>
       <c r="F80" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 4</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G80" s="36" t="n">
-        <v>2000</v>
+        <v>450</v>
       </c>
       <c r="H80" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr">
@@ -7566,31 +7570,39 @@
     </row>
     <row r="81">
       <c r="A81" s="38" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B81" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
-        </is>
-      </c>
-      <c r="D81" s="31" t="inlineStr"/>
-      <c r="E81" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2025-05</t>
+        </is>
+      </c>
       <c r="F81" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Fatura de horas · 5</t>
         </is>
       </c>
       <c r="G81" s="36" t="n">
-        <v>450</v>
+        <v>1800</v>
       </c>
       <c r="H81" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr">
@@ -7618,26 +7630,26 @@
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E82" s="31" t="inlineStr">
         <is>
-          <t>CONS-2025-05</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F82" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 5</t>
+          <t>Fatura de horas · 4</t>
         </is>
       </c>
       <c r="G82" s="36" t="n">
-        <v>1800</v>
+        <v>3060</v>
       </c>
       <c r="H82" s="32" t="inlineStr">
         <is>
@@ -7664,31 +7676,23 @@
       </c>
       <c r="B83" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
-        </is>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>9362688-24.2025.8.26.0436</t>
-        </is>
-      </c>
+          <t>Contador</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr"/>
+      <c r="E83" s="31" t="inlineStr"/>
       <c r="F83" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 4</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G83" s="36" t="n">
-        <v>3060</v>
+        <v>600</v>
       </c>
       <c r="H83" s="32" t="inlineStr">
         <is>
@@ -7720,22 +7724,22 @@
       </c>
       <c r="C84" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
+          <t>Pró-labore dos sócios</t>
         </is>
       </c>
       <c r="D84" s="31" t="inlineStr"/>
       <c r="E84" s="31" t="inlineStr"/>
       <c r="F84" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Distribuição de lucro · 1º trimestre · Marina Ferraz</t>
         </is>
       </c>
       <c r="G84" s="36" t="n">
-        <v>600</v>
+        <v>2655</v>
       </c>
       <c r="H84" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I84" s="32" t="inlineStr">
@@ -7770,11 +7774,11 @@
       <c r="E85" s="31" t="inlineStr"/>
       <c r="F85" s="31" t="inlineStr">
         <is>
-          <t>Distribuição de lucro · 1º trimestre · Marina Ferraz</t>
+          <t>Distribuição de lucro · 1º trimestre · Rafael Lima</t>
         </is>
       </c>
       <c r="G85" s="36" t="n">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="H85" s="32" t="inlineStr">
         <is>
@@ -7797,7 +7801,7 @@
     </row>
     <row r="86">
       <c r="A86" s="38" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="B86" s="32" t="inlineStr">
         <is>
@@ -7806,22 +7810,22 @@
       </c>
       <c r="C86" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="D86" s="31" t="inlineStr"/>
       <c r="E86" s="31" t="inlineStr"/>
       <c r="F86" s="31" t="inlineStr">
         <is>
-          <t>Distribuição de lucro · 1º trimestre · Rafael Lima</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G86" s="36" t="n">
-        <v>2656</v>
+        <v>220</v>
       </c>
       <c r="H86" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I86" s="32" t="inlineStr">
@@ -7840,31 +7844,39 @@
     </row>
     <row r="87">
       <c r="A87" s="38" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B87" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
-        </is>
-      </c>
-      <c r="D87" s="31" t="inlineStr"/>
-      <c r="E87" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D87" s="31" t="inlineStr">
+        <is>
+          <t>Agência Prisma</t>
+        </is>
+      </c>
+      <c r="E87" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-07</t>
+        </is>
+      </c>
       <c r="F87" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G87" s="36" t="n">
-        <v>220</v>
+        <v>3500</v>
       </c>
       <c r="H87" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I87" s="32" t="inlineStr">
@@ -7892,26 +7904,26 @@
       </c>
       <c r="C88" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D88" s="31" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="E88" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-07</t>
+          <t>8663770-96.2025.8.26.0481</t>
         </is>
       </c>
       <c r="F88" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Honorários · parcela 11</t>
         </is>
       </c>
       <c r="G88" s="36" t="n">
-        <v>3500</v>
+        <v>800</v>
       </c>
       <c r="H88" s="32" t="inlineStr">
         <is>
@@ -7934,7 +7946,7 @@
     </row>
     <row r="89">
       <c r="A89" s="38" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B89" s="32" t="inlineStr">
         <is>
@@ -7943,26 +7955,18 @@
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D89" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E89" s="31" t="inlineStr">
-        <is>
-          <t>8663770-96.2025.8.26.0481</t>
-        </is>
-      </c>
+          <t>Outras entradas</t>
+        </is>
+      </c>
+      <c r="D89" s="31" t="inlineStr"/>
+      <c r="E89" s="31" t="inlineStr"/>
       <c r="F89" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 11</t>
+          <t>Devolução de despesa pessoal · Marina Ferraz</t>
         </is>
       </c>
       <c r="G89" s="36" t="n">
-        <v>800</v>
+        <v>480</v>
       </c>
       <c r="H89" s="32" t="inlineStr">
         <is>
@@ -7985,7 +7989,7 @@
     </row>
     <row r="90">
       <c r="A90" s="38" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B90" s="32" t="inlineStr">
         <is>
@@ -7994,18 +7998,26 @@
       </c>
       <c r="C90" s="31" t="inlineStr">
         <is>
-          <t>Outras entradas</t>
-        </is>
-      </c>
-      <c r="D90" s="31" t="inlineStr"/>
-      <c r="E90" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D90" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Nunes</t>
+        </is>
+      </c>
+      <c r="E90" s="31" t="inlineStr">
+        <is>
+          <t>8045862-82.2026.8.26.0491</t>
+        </is>
+      </c>
       <c r="F90" s="31" t="inlineStr">
         <is>
-          <t>Devolução de despesa pessoal · Marina Ferraz</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G90" s="36" t="n">
-        <v>480</v>
+        <v>1800</v>
       </c>
       <c r="H90" s="32" t="inlineStr">
         <is>
@@ -8032,35 +8044,27 @@
       </c>
       <c r="B91" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D91" s="31" t="inlineStr">
-        <is>
-          <t>Carlos Eduardo Nunes</t>
-        </is>
-      </c>
-      <c r="E91" s="31" t="inlineStr">
-        <is>
-          <t>8045862-82.2026.8.26.0491</t>
-        </is>
-      </c>
+          <t>Anuidades OAB e cursos</t>
+        </is>
+      </c>
+      <c r="D91" s="31" t="inlineStr"/>
+      <c r="E91" s="31" t="inlineStr"/>
       <c r="F91" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G91" s="36" t="n">
-        <v>1800</v>
+        <v>250</v>
       </c>
       <c r="H91" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I91" s="32" t="inlineStr">
@@ -8079,7 +8083,7 @@
     </row>
     <row r="92">
       <c r="A92" s="38" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B92" s="32" t="inlineStr">
         <is>
@@ -8088,22 +8092,30 @@
       </c>
       <c r="C92" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
-        </is>
-      </c>
-      <c r="D92" s="31" t="inlineStr"/>
-      <c r="E92" s="31" t="inlineStr"/>
+          <t>Custas e despesas de processo</t>
+        </is>
+      </c>
+      <c r="D92" s="31" t="inlineStr">
+        <is>
+          <t>Agência Prisma</t>
+        </is>
+      </c>
+      <c r="E92" s="31" t="inlineStr">
+        <is>
+          <t>9362688-24.2025.8.26.0436</t>
+        </is>
+      </c>
       <c r="F92" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Custas de recurso</t>
         </is>
       </c>
       <c r="G92" s="36" t="n">
-        <v>250</v>
+        <v>540</v>
       </c>
       <c r="H92" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I92" s="32" t="inlineStr">
@@ -8122,35 +8134,35 @@
     </row>
     <row r="93">
       <c r="A93" s="38" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B93" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D93" s="31" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="E93" s="31" t="inlineStr">
         <is>
-          <t>9362688-24.2025.8.26.0436</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="F93" s="31" t="inlineStr">
         <is>
-          <t>Custas de recurso</t>
+          <t>Honorários · parcela 3 (vencida)</t>
         </is>
       </c>
       <c r="G93" s="36" t="n">
-        <v>540</v>
+        <v>2100</v>
       </c>
       <c r="H93" s="32" t="inlineStr">
         <is>
@@ -8159,7 +8171,7 @@
       </c>
       <c r="I93" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J93" s="35">
@@ -8173,44 +8185,36 @@
     </row>
     <row r="94">
       <c r="A94" s="38" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B94" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C94" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D94" s="31" t="inlineStr">
-        <is>
-          <t>Bistrô 42</t>
-        </is>
-      </c>
-      <c r="E94" s="31" t="inlineStr">
-        <is>
-          <t>8056747-83.2026.8.26.0561</t>
-        </is>
-      </c>
+          <t>Material, correio e outros</t>
+        </is>
+      </c>
+      <c r="D94" s="31" t="inlineStr"/>
+      <c r="E94" s="31" t="inlineStr"/>
       <c r="F94" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3 (vencida)</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G94" s="36" t="n">
-        <v>2100</v>
+        <v>380</v>
       </c>
       <c r="H94" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I94" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J94" s="35">
@@ -8224,31 +8228,39 @@
     </row>
     <row r="95">
       <c r="A95" s="38" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="B95" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D95" s="31" t="inlineStr"/>
-      <c r="E95" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D95" s="31" t="inlineStr">
+        <is>
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="inlineStr">
+        <is>
+          <t>6184138-13.2026.8.26.0378</t>
+        </is>
+      </c>
       <c r="F95" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G95" s="36" t="n">
-        <v>380</v>
+        <v>3000</v>
       </c>
       <c r="H95" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I95" s="32" t="inlineStr">
@@ -8271,35 +8283,27 @@
       </c>
       <c r="B96" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C96" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D96" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E96" s="31" t="inlineStr">
-        <is>
-          <t>6184138-13.2026.8.26.0378</t>
-        </is>
-      </c>
+          <t>Impostos e taxas</t>
+        </is>
+      </c>
+      <c r="D96" s="31" t="inlineStr"/>
+      <c r="E96" s="31" t="inlineStr"/>
       <c r="F96" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G96" s="36" t="n">
-        <v>3000</v>
+        <v>2287</v>
       </c>
       <c r="H96" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I96" s="32" t="inlineStr">
@@ -8327,22 +8331,22 @@
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D97" s="31" t="inlineStr"/>
       <c r="E97" s="31" t="inlineStr"/>
       <c r="F97" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G97" s="36" t="n">
-        <v>2287</v>
+        <v>400</v>
       </c>
       <c r="H97" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I97" s="32" t="inlineStr">
@@ -8361,31 +8365,39 @@
     </row>
     <row r="98">
       <c r="A98" s="38" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B98" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C98" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
-        </is>
-      </c>
-      <c r="D98" s="31" t="inlineStr"/>
-      <c r="E98" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D98" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="E98" s="31" t="inlineStr">
+        <is>
+          <t>6832730-55.2026.8.26.0386</t>
+        </is>
+      </c>
       <c r="F98" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G98" s="36" t="n">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="H98" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I98" s="32" t="inlineStr">
@@ -8404,7 +8416,7 @@
     </row>
     <row r="99">
       <c r="A99" s="38" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B99" s="32" t="inlineStr">
         <is>
@@ -8418,21 +8430,21 @@
       </c>
       <c r="D99" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="E99" s="31" t="inlineStr">
         <is>
-          <t>6832730-55.2026.8.26.0386</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="F99" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Honorários · parcela 5</t>
         </is>
       </c>
       <c r="G99" s="36" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="H99" s="32" t="inlineStr">
         <is>
@@ -8455,39 +8467,31 @@
     </row>
     <row r="100">
       <c r="A100" s="38" t="n">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="B100" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C100" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D100" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E100" s="31" t="inlineStr">
-        <is>
-          <t>3363714-92.2025.8.26.0592</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D100" s="31" t="inlineStr"/>
+      <c r="E100" s="31" t="inlineStr"/>
       <c r="F100" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 5</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G100" s="36" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H100" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I100" s="32" t="inlineStr">
@@ -8522,7 +8526,7 @@
       <c r="E101" s="31" t="inlineStr"/>
       <c r="F101" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G101" s="36" t="n">
@@ -8549,7 +8553,7 @@
     </row>
     <row r="102">
       <c r="A102" s="38" t="n">
-        <v>46140</v>
+        <v>46147</v>
       </c>
       <c r="B102" s="32" t="inlineStr">
         <is>
@@ -8558,22 +8562,22 @@
       </c>
       <c r="C102" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
+          <t>Aluguel e condomínio</t>
         </is>
       </c>
       <c r="D102" s="31" t="inlineStr"/>
       <c r="E102" s="31" t="inlineStr"/>
       <c r="F102" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G102" s="36" t="n">
-        <v>6000</v>
+        <v>2800</v>
       </c>
       <c r="H102" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I102" s="32" t="inlineStr">
@@ -8583,7 +8587,7 @@
       </c>
       <c r="J102" s="35">
         <f>IF(A102="","",MONTH(A102))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K102" s="35">
         <f>IF(A102="","",YEAR(A102))</f>
@@ -8601,22 +8605,22 @@
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
+          <t>Estagiária (bolsa)</t>
         </is>
       </c>
       <c r="D103" s="31" t="inlineStr"/>
       <c r="E103" s="31" t="inlineStr"/>
       <c r="F103" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G103" s="36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H103" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I103" s="32" t="inlineStr">
@@ -8635,7 +8639,7 @@
     </row>
     <row r="104">
       <c r="A104" s="38" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B104" s="32" t="inlineStr">
         <is>
@@ -8644,22 +8648,30 @@
       </c>
       <c r="C104" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
-        </is>
-      </c>
-      <c r="D104" s="31" t="inlineStr"/>
-      <c r="E104" s="31" t="inlineStr"/>
+          <t>Custas e despesas de processo</t>
+        </is>
+      </c>
+      <c r="D104" s="31" t="inlineStr">
+        <is>
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="E104" s="31" t="inlineStr">
+        <is>
+          <t>6184138-13.2026.8.26.0378</t>
+        </is>
+      </c>
       <c r="F104" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Custas de distribuição</t>
         </is>
       </c>
       <c r="G104" s="36" t="n">
-        <v>1400</v>
+        <v>310</v>
       </c>
       <c r="H104" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I104" s="32" t="inlineStr">
@@ -8687,26 +8699,18 @@
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
-        </is>
-      </c>
-      <c r="D105" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E105" s="31" t="inlineStr">
-        <is>
-          <t>6184138-13.2026.8.26.0378</t>
-        </is>
-      </c>
+          <t>Outras saídas</t>
+        </is>
+      </c>
+      <c r="D105" s="31" t="inlineStr"/>
+      <c r="E105" s="31" t="inlineStr"/>
       <c r="F105" s="31" t="inlineStr">
         <is>
-          <t>Custas de distribuição</t>
+          <t>Despesa pessoal · Marina Ferraz · plano de saúde particular (a acertar)</t>
         </is>
       </c>
       <c r="G105" s="36" t="n">
-        <v>310</v>
+        <v>480</v>
       </c>
       <c r="H105" s="32" t="inlineStr">
         <is>
@@ -8729,31 +8733,39 @@
     </row>
     <row r="106">
       <c r="A106" s="38" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B106" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C106" s="31" t="inlineStr">
         <is>
-          <t>Outras saídas</t>
-        </is>
-      </c>
-      <c r="D106" s="31" t="inlineStr"/>
-      <c r="E106" s="31" t="inlineStr"/>
+          <t>Honorários de êxito</t>
+        </is>
+      </c>
+      <c r="D106" s="31" t="inlineStr">
+        <is>
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="E106" s="31" t="inlineStr">
+        <is>
+          <t>9778116-95.2025.8.26.0106</t>
+        </is>
+      </c>
       <c r="F106" s="31" t="inlineStr">
         <is>
-          <t>Despesa pessoal · Marina Ferraz · plano de saúde particular (a acertar)</t>
+          <t>Honorários de êxito (fim do caso)</t>
         </is>
       </c>
       <c r="G106" s="36" t="n">
-        <v>480</v>
+        <v>9000</v>
       </c>
       <c r="H106" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I106" s="32" t="inlineStr">
@@ -8776,35 +8788,27 @@
       </c>
       <c r="B107" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>Honorários de êxito</t>
-        </is>
-      </c>
-      <c r="D107" s="31" t="inlineStr">
-        <is>
-          <t>Construtora Horizonte</t>
-        </is>
-      </c>
-      <c r="E107" s="31" t="inlineStr">
-        <is>
-          <t>9778116-95.2025.8.26.0106</t>
-        </is>
-      </c>
+          <t>Sistemas e assinaturas</t>
+        </is>
+      </c>
+      <c r="D107" s="31" t="inlineStr"/>
+      <c r="E107" s="31" t="inlineStr"/>
       <c r="F107" s="31" t="inlineStr">
         <is>
-          <t>Honorários de êxito (fim do caso)</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G107" s="36" t="n">
-        <v>9000</v>
+        <v>450</v>
       </c>
       <c r="H107" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I107" s="32" t="inlineStr">
@@ -8823,7 +8827,7 @@
     </row>
     <row r="108">
       <c r="A108" s="38" t="n">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="B108" s="32" t="inlineStr">
         <is>
@@ -8832,22 +8836,22 @@
       </c>
       <c r="C108" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Contador</t>
         </is>
       </c>
       <c r="D108" s="31" t="inlineStr"/>
       <c r="E108" s="31" t="inlineStr"/>
       <c r="F108" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G108" s="36" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="H108" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I108" s="32" t="inlineStr">
@@ -8866,27 +8870,35 @@
     </row>
     <row r="109">
       <c r="A109" s="38" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B109" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
-        </is>
-      </c>
-      <c r="D109" s="31" t="inlineStr"/>
-      <c r="E109" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D109" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="E109" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2025-05</t>
+        </is>
+      </c>
       <c r="F109" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Fatura de horas · 6</t>
         </is>
       </c>
       <c r="G109" s="36" t="n">
-        <v>600</v>
+        <v>2160</v>
       </c>
       <c r="H109" s="32" t="inlineStr">
         <is>
@@ -8918,30 +8930,30 @@
       </c>
       <c r="C110" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D110" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="E110" s="31" t="inlineStr">
         <is>
-          <t>CONS-2025-05</t>
+          <t>2354318-24.2026.8.26.0295</t>
         </is>
       </c>
       <c r="F110" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 6</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G110" s="36" t="n">
-        <v>2160</v>
+        <v>3000</v>
       </c>
       <c r="H110" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I110" s="32" t="inlineStr">
@@ -8969,30 +8981,30 @@
       </c>
       <c r="C111" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D111" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E111" s="31" t="inlineStr">
         <is>
-          <t>2354318-24.2026.8.26.0295</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F111" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Fatura de horas · 5</t>
         </is>
       </c>
       <c r="G111" s="36" t="n">
-        <v>3000</v>
+        <v>2160</v>
       </c>
       <c r="H111" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I111" s="32" t="inlineStr">
@@ -9011,7 +9023,7 @@
     </row>
     <row r="112">
       <c r="A112" s="38" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B112" s="32" t="inlineStr">
         <is>
@@ -9020,30 +9032,30 @@
       </c>
       <c r="C112" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D112" s="31" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="E112" s="31" t="inlineStr">
         <is>
-          <t>9362688-24.2025.8.26.0436</t>
+          <t>8663770-96.2025.8.26.0481</t>
         </is>
       </c>
       <c r="F112" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 5</t>
+          <t>Honorários · parcela 12</t>
         </is>
       </c>
       <c r="G112" s="36" t="n">
-        <v>2160</v>
+        <v>800</v>
       </c>
       <c r="H112" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I112" s="32" t="inlineStr">
@@ -9066,35 +9078,27 @@
       </c>
       <c r="B113" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C113" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D113" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E113" s="31" t="inlineStr">
-        <is>
-          <t>8663770-96.2025.8.26.0481</t>
-        </is>
-      </c>
+          <t>Deslocamento e viagens</t>
+        </is>
+      </c>
+      <c r="D113" s="31" t="inlineStr"/>
+      <c r="E113" s="31" t="inlineStr"/>
       <c r="F113" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 12</t>
+          <t>Combustível e estacionamento (audiências)</t>
         </is>
       </c>
       <c r="G113" s="36" t="n">
-        <v>800</v>
+        <v>310</v>
       </c>
       <c r="H113" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I113" s="32" t="inlineStr">
@@ -9122,22 +9126,22 @@
       </c>
       <c r="C114" s="31" t="inlineStr">
         <is>
-          <t>Deslocamento e viagens</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="D114" s="31" t="inlineStr"/>
       <c r="E114" s="31" t="inlineStr"/>
       <c r="F114" s="31" t="inlineStr">
         <is>
-          <t>Combustível e estacionamento (audiências)</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G114" s="36" t="n">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="H114" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I114" s="32" t="inlineStr">
@@ -9156,7 +9160,7 @@
     </row>
     <row r="115">
       <c r="A115" s="38" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B115" s="32" t="inlineStr">
         <is>
@@ -9165,22 +9169,22 @@
       </c>
       <c r="C115" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="D115" s="31" t="inlineStr"/>
       <c r="E115" s="31" t="inlineStr"/>
       <c r="F115" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G115" s="36" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="H115" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I115" s="32" t="inlineStr">
@@ -9199,7 +9203,7 @@
     </row>
     <row r="116">
       <c r="A116" s="38" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B116" s="32" t="inlineStr">
         <is>
@@ -9208,18 +9212,18 @@
       </c>
       <c r="C116" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="D116" s="31" t="inlineStr"/>
       <c r="E116" s="31" t="inlineStr"/>
       <c r="F116" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G116" s="36" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="H116" s="32" t="inlineStr">
         <is>
@@ -9242,31 +9246,39 @@
     </row>
     <row r="117">
       <c r="A117" s="38" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B117" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C117" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D117" s="31" t="inlineStr"/>
-      <c r="E117" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D117" s="31" t="inlineStr">
+        <is>
+          <t>Agência Prisma</t>
+        </is>
+      </c>
+      <c r="E117" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-07</t>
+        </is>
+      </c>
       <c r="F117" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G117" s="36" t="n">
-        <v>380</v>
+        <v>3500</v>
       </c>
       <c r="H117" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I117" s="32" t="inlineStr">
@@ -9289,35 +9301,27 @@
       </c>
       <c r="B118" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C118" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
-        </is>
-      </c>
-      <c r="D118" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E118" s="31" t="inlineStr">
-        <is>
-          <t>CONS-2026-07</t>
-        </is>
-      </c>
+          <t>Impostos e taxas</t>
+        </is>
+      </c>
+      <c r="D118" s="31" t="inlineStr"/>
+      <c r="E118" s="31" t="inlineStr"/>
       <c r="F118" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G118" s="36" t="n">
-        <v>3500</v>
+        <v>1581</v>
       </c>
       <c r="H118" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I118" s="32" t="inlineStr">
@@ -9345,22 +9349,22 @@
       </c>
       <c r="C119" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D119" s="31" t="inlineStr"/>
       <c r="E119" s="31" t="inlineStr"/>
       <c r="F119" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G119" s="36" t="n">
-        <v>1581</v>
+        <v>400</v>
       </c>
       <c r="H119" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I119" s="32" t="inlineStr">
@@ -9379,31 +9383,39 @@
     </row>
     <row r="120">
       <c r="A120" s="38" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B120" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C120" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
-        </is>
-      </c>
-      <c r="D120" s="31" t="inlineStr"/>
-      <c r="E120" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D120" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="E120" s="31" t="inlineStr">
+        <is>
+          <t>6832730-55.2026.8.26.0386</t>
+        </is>
+      </c>
       <c r="F120" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G120" s="36" t="n">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="H120" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I120" s="32" t="inlineStr">
@@ -9422,7 +9434,7 @@
     </row>
     <row r="121">
       <c r="A121" s="38" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B121" s="32" t="inlineStr">
         <is>
@@ -9436,21 +9448,21 @@
       </c>
       <c r="D121" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="E121" s="31" t="inlineStr">
         <is>
-          <t>6832730-55.2026.8.26.0386</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="F121" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G121" s="36" t="n">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="H121" s="32" t="inlineStr">
         <is>
@@ -9473,7 +9485,7 @@
     </row>
     <row r="122">
       <c r="A122" s="38" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B122" s="32" t="inlineStr">
         <is>
@@ -9487,21 +9499,21 @@
       </c>
       <c r="D122" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="E122" s="31" t="inlineStr">
         <is>
-          <t>2645033-67.2026.8.26.0012</t>
+          <t>6184138-13.2026.8.26.0378</t>
         </is>
       </c>
       <c r="F122" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G122" s="36" t="n">
-        <v>7200</v>
+        <v>1500</v>
       </c>
       <c r="H122" s="32" t="inlineStr">
         <is>
@@ -9524,39 +9536,31 @@
     </row>
     <row r="123">
       <c r="A123" s="38" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B123" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C123" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D123" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E123" s="31" t="inlineStr">
-        <is>
-          <t>6184138-13.2026.8.26.0378</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D123" s="31" t="inlineStr"/>
+      <c r="E123" s="31" t="inlineStr"/>
       <c r="F123" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G123" s="36" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="H123" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I123" s="32" t="inlineStr">
@@ -9591,7 +9595,7 @@
       <c r="E124" s="31" t="inlineStr"/>
       <c r="F124" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G124" s="36" t="n">
@@ -9618,31 +9622,39 @@
     </row>
     <row r="125">
       <c r="A125" s="38" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B125" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C125" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D125" s="31" t="inlineStr"/>
-      <c r="E125" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D125" s="31" t="inlineStr">
+        <is>
+          <t>Luciana Farias</t>
+        </is>
+      </c>
+      <c r="E125" s="31" t="inlineStr">
+        <is>
+          <t>7099226-69.2026.8.26.0433</t>
+        </is>
+      </c>
       <c r="F125" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G125" s="36" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="H125" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I125" s="32" t="inlineStr">
@@ -9652,7 +9664,7 @@
       </c>
       <c r="J125" s="35">
         <f>IF(A125="","",MONTH(A125))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K125" s="35">
         <f>IF(A125="","",YEAR(A125))</f>
@@ -9661,39 +9673,31 @@
     </row>
     <row r="126">
       <c r="A126" s="38" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B126" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C126" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D126" s="31" t="inlineStr">
-        <is>
-          <t>Luciana Farias</t>
-        </is>
-      </c>
-      <c r="E126" s="31" t="inlineStr">
-        <is>
-          <t>7099226-69.2026.8.26.0433</t>
-        </is>
-      </c>
+          <t>Aluguel e condomínio</t>
+        </is>
+      </c>
+      <c r="D126" s="31" t="inlineStr"/>
+      <c r="E126" s="31" t="inlineStr"/>
       <c r="F126" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G126" s="36" t="n">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="H126" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I126" s="32" t="inlineStr">
@@ -9721,22 +9725,22 @@
       </c>
       <c r="C127" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
+          <t>Estagiária (bolsa)</t>
         </is>
       </c>
       <c r="D127" s="31" t="inlineStr"/>
       <c r="E127" s="31" t="inlineStr"/>
       <c r="F127" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G127" s="36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H127" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I127" s="32" t="inlineStr">
@@ -9755,31 +9759,39 @@
     </row>
     <row r="128">
       <c r="A128" s="38" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B128" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C128" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
-        </is>
-      </c>
-      <c r="D128" s="31" t="inlineStr"/>
-      <c r="E128" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D128" s="31" t="inlineStr">
+        <is>
+          <t>Marcos Vinícius Teles</t>
+        </is>
+      </c>
+      <c r="E128" s="31" t="inlineStr">
+        <is>
+          <t>9605863-76.2026.8.26.0026</t>
+        </is>
+      </c>
       <c r="F128" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G128" s="36" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="H128" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I128" s="32" t="inlineStr">
@@ -9802,35 +9814,35 @@
       </c>
       <c r="B129" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C129" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Custas e despesas de processo</t>
         </is>
       </c>
       <c r="D129" s="31" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="E129" s="31" t="inlineStr">
         <is>
-          <t>9605863-76.2026.8.26.0026</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="F129" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Certidões e cópias</t>
         </is>
       </c>
       <c r="G129" s="36" t="n">
-        <v>2400</v>
+        <v>95</v>
       </c>
       <c r="H129" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I129" s="32" t="inlineStr">
@@ -9858,30 +9870,22 @@
       </c>
       <c r="C130" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
-        </is>
-      </c>
-      <c r="D130" s="31" t="inlineStr">
-        <is>
-          <t>Bistrô 42</t>
-        </is>
-      </c>
-      <c r="E130" s="31" t="inlineStr">
-        <is>
-          <t>8056747-83.2026.8.26.0561</t>
-        </is>
-      </c>
+          <t>Sistemas e assinaturas</t>
+        </is>
+      </c>
+      <c r="D130" s="31" t="inlineStr"/>
+      <c r="E130" s="31" t="inlineStr"/>
       <c r="F130" s="31" t="inlineStr">
         <is>
-          <t>Certidões e cópias</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G130" s="36" t="n">
-        <v>95</v>
+        <v>450</v>
       </c>
       <c r="H130" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I130" s="32" t="inlineStr">
@@ -9900,31 +9904,39 @@
     </row>
     <row r="131">
       <c r="A131" s="38" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B131" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C131" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
-        </is>
-      </c>
-      <c r="D131" s="31" t="inlineStr"/>
-      <c r="E131" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D131" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="E131" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2025-05</t>
+        </is>
+      </c>
       <c r="F131" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Fatura de horas · 7</t>
         </is>
       </c>
       <c r="G131" s="36" t="n">
-        <v>450</v>
+        <v>1620</v>
       </c>
       <c r="H131" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I131" s="32" t="inlineStr">
@@ -9952,30 +9964,30 @@
       </c>
       <c r="C132" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D132" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="E132" s="31" t="inlineStr">
         <is>
-          <t>CONS-2025-05</t>
+          <t>2354318-24.2026.8.26.0295</t>
         </is>
       </c>
       <c r="F132" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 7</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G132" s="36" t="n">
-        <v>1620</v>
+        <v>2100</v>
       </c>
       <c r="H132" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I132" s="32" t="inlineStr">
@@ -10003,30 +10015,30 @@
       </c>
       <c r="C133" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D133" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E133" s="31" t="inlineStr">
         <is>
-          <t>2354318-24.2026.8.26.0295</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F133" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Fatura de horas · 6</t>
         </is>
       </c>
       <c r="G133" s="36" t="n">
-        <v>2100</v>
+        <v>2700</v>
       </c>
       <c r="H133" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I133" s="32" t="inlineStr">
@@ -10049,31 +10061,23 @@
       </c>
       <c r="B134" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C134" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
-        </is>
-      </c>
-      <c r="D134" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E134" s="31" t="inlineStr">
-        <is>
-          <t>9362688-24.2025.8.26.0436</t>
-        </is>
-      </c>
+          <t>Contador</t>
+        </is>
+      </c>
+      <c r="D134" s="31" t="inlineStr"/>
+      <c r="E134" s="31" t="inlineStr"/>
       <c r="F134" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 6</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G134" s="36" t="n">
-        <v>2700</v>
+        <v>600</v>
       </c>
       <c r="H134" s="32" t="inlineStr">
         <is>
@@ -10096,7 +10100,7 @@
     </row>
     <row r="135">
       <c r="A135" s="38" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B135" s="32" t="inlineStr">
         <is>
@@ -10105,18 +10109,18 @@
       </c>
       <c r="C135" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="D135" s="31" t="inlineStr"/>
       <c r="E135" s="31" t="inlineStr"/>
       <c r="F135" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G135" s="36" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="H135" s="32" t="inlineStr">
         <is>
@@ -10139,31 +10143,39 @@
     </row>
     <row r="136">
       <c r="A136" s="38" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B136" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C136" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
-        </is>
-      </c>
-      <c r="D136" s="31" t="inlineStr"/>
-      <c r="E136" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D136" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="E136" s="31" t="inlineStr">
+        <is>
+          <t>9616569-91.2026.8.26.0079</t>
+        </is>
+      </c>
       <c r="F136" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G136" s="36" t="n">
-        <v>220</v>
+        <v>2400</v>
       </c>
       <c r="H136" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I136" s="32" t="inlineStr">
@@ -10186,35 +10198,27 @@
       </c>
       <c r="B137" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C137" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D137" s="31" t="inlineStr">
-        <is>
-          <t>Patrícia Gomes</t>
-        </is>
-      </c>
-      <c r="E137" s="31" t="inlineStr">
-        <is>
-          <t>9616569-91.2026.8.26.0079</t>
-        </is>
-      </c>
+          <t>Anuidades OAB e cursos</t>
+        </is>
+      </c>
+      <c r="D137" s="31" t="inlineStr"/>
+      <c r="E137" s="31" t="inlineStr"/>
       <c r="F137" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G137" s="36" t="n">
-        <v>2400</v>
+        <v>250</v>
       </c>
       <c r="H137" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I137" s="32" t="inlineStr">
@@ -10233,7 +10237,7 @@
     </row>
     <row r="138">
       <c r="A138" s="38" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B138" s="32" t="inlineStr">
         <is>
@@ -10242,18 +10246,18 @@
       </c>
       <c r="C138" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="D138" s="31" t="inlineStr"/>
       <c r="E138" s="31" t="inlineStr"/>
       <c r="F138" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G138" s="36" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="H138" s="32" t="inlineStr">
         <is>
@@ -10276,36 +10280,44 @@
     </row>
     <row r="139">
       <c r="A139" s="38" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B139" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C139" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D139" s="31" t="inlineStr"/>
-      <c r="E139" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D139" s="31" t="inlineStr">
+        <is>
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="E139" s="31" t="inlineStr">
+        <is>
+          <t>6184138-13.2026.8.26.0378</t>
+        </is>
+      </c>
       <c r="F139" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários · parcela 2 (vencida)</t>
         </is>
       </c>
       <c r="G139" s="36" t="n">
-        <v>380</v>
+        <v>1500</v>
       </c>
       <c r="H139" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I139" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J139" s="35">
@@ -10323,40 +10335,32 @@
       </c>
       <c r="B140" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C140" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D140" s="31" t="inlineStr">
-        <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="E140" s="31" t="inlineStr">
-        <is>
-          <t>6184138-13.2026.8.26.0378</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D140" s="31" t="inlineStr"/>
+      <c r="E140" s="31" t="inlineStr"/>
       <c r="F140" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2 (vencida)</t>
+          <t>Retirada extra · Marina Ferraz · reforma em casa</t>
         </is>
       </c>
       <c r="G140" s="36" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="H140" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I140" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J140" s="35">
@@ -10370,7 +10374,7 @@
     </row>
     <row r="141">
       <c r="A141" s="38" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B141" s="32" t="inlineStr">
         <is>
@@ -10379,22 +10383,22 @@
       </c>
       <c r="C141" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
+          <t>Impostos e taxas</t>
         </is>
       </c>
       <c r="D141" s="31" t="inlineStr"/>
       <c r="E141" s="31" t="inlineStr"/>
       <c r="F141" s="31" t="inlineStr">
         <is>
-          <t>Retirada extra · Marina Ferraz · reforma em casa</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G141" s="36" t="n">
-        <v>2000</v>
+        <v>2490</v>
       </c>
       <c r="H141" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I141" s="32" t="inlineStr">
@@ -10422,22 +10426,22 @@
       </c>
       <c r="C142" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D142" s="31" t="inlineStr"/>
       <c r="E142" s="31" t="inlineStr"/>
       <c r="F142" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G142" s="36" t="n">
-        <v>2490</v>
+        <v>400</v>
       </c>
       <c r="H142" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I142" s="32" t="inlineStr">
@@ -10456,31 +10460,39 @@
     </row>
     <row r="143">
       <c r="A143" s="38" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="B143" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C143" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
-        </is>
-      </c>
-      <c r="D143" s="31" t="inlineStr"/>
-      <c r="E143" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D143" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="E143" s="31" t="inlineStr">
+        <is>
+          <t>2645033-67.2026.8.26.0012</t>
+        </is>
+      </c>
       <c r="F143" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G143" s="36" t="n">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="H143" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I143" s="32" t="inlineStr">
@@ -10499,39 +10511,31 @@
     </row>
     <row r="144">
       <c r="A144" s="38" t="n">
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="B144" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C144" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D144" s="31" t="inlineStr">
-        <is>
-          <t>Clínica Bem-Estar</t>
-        </is>
-      </c>
-      <c r="E144" s="31" t="inlineStr">
-        <is>
-          <t>2645033-67.2026.8.26.0012</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D144" s="31" t="inlineStr"/>
+      <c r="E144" s="31" t="inlineStr"/>
       <c r="F144" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G144" s="36" t="n">
-        <v>2700</v>
+        <v>6000</v>
       </c>
       <c r="H144" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I144" s="32" t="inlineStr">
@@ -10566,7 +10570,7 @@
       <c r="E145" s="31" t="inlineStr"/>
       <c r="F145" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G145" s="36" t="n">
@@ -10593,31 +10597,39 @@
     </row>
     <row r="146">
       <c r="A146" s="38" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B146" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C146" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D146" s="31" t="inlineStr"/>
-      <c r="E146" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D146" s="31" t="inlineStr">
+        <is>
+          <t>Helena Duarte</t>
+        </is>
+      </c>
+      <c r="E146" s="31" t="inlineStr">
+        <is>
+          <t>7679821-77.2026.8.26.0265</t>
+        </is>
+      </c>
       <c r="F146" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G146" s="36" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="H146" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I146" s="32" t="inlineStr">
@@ -10636,7 +10648,7 @@
     </row>
     <row r="147">
       <c r="A147" s="38" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B147" s="32" t="inlineStr">
         <is>
@@ -10645,26 +10657,26 @@
       </c>
       <c r="C147" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Honorários de êxito</t>
         </is>
       </c>
       <c r="D147" s="31" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="E147" s="31" t="inlineStr">
         <is>
-          <t>7679821-77.2026.8.26.0265</t>
+          <t>6161129-80.2025.8.26.0663</t>
         </is>
       </c>
       <c r="F147" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Honorários de êxito (fim do caso)</t>
         </is>
       </c>
       <c r="G147" s="36" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H147" s="32" t="inlineStr">
         <is>
@@ -10687,7 +10699,7 @@
     </row>
     <row r="148">
       <c r="A148" s="38" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B148" s="32" t="inlineStr">
         <is>
@@ -10696,26 +10708,26 @@
       </c>
       <c r="C148" s="31" t="inlineStr">
         <is>
-          <t>Honorários de êxito</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D148" s="31" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="E148" s="31" t="inlineStr">
         <is>
-          <t>6161129-80.2025.8.26.0663</t>
+          <t>7099226-69.2026.8.26.0433</t>
         </is>
       </c>
       <c r="F148" s="31" t="inlineStr">
         <is>
-          <t>Honorários de êxito (fim do caso)</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G148" s="36" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="H148" s="32" t="inlineStr">
         <is>
@@ -10729,7 +10741,7 @@
       </c>
       <c r="J148" s="35">
         <f>IF(A148="","",MONTH(A148))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K148" s="35">
         <f>IF(A148="","",YEAR(A148))</f>
@@ -10738,39 +10750,31 @@
     </row>
     <row r="149">
       <c r="A149" s="38" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="B149" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C149" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D149" s="31" t="inlineStr">
-        <is>
-          <t>Luciana Farias</t>
-        </is>
-      </c>
-      <c r="E149" s="31" t="inlineStr">
-        <is>
-          <t>7099226-69.2026.8.26.0433</t>
-        </is>
-      </c>
+          <t>Aluguel e condomínio</t>
+        </is>
+      </c>
+      <c r="D149" s="31" t="inlineStr"/>
+      <c r="E149" s="31" t="inlineStr"/>
       <c r="F149" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G149" s="36" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="H149" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I149" s="32" t="inlineStr">
@@ -10798,22 +10802,22 @@
       </c>
       <c r="C150" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
+          <t>Estagiária (bolsa)</t>
         </is>
       </c>
       <c r="D150" s="31" t="inlineStr"/>
       <c r="E150" s="31" t="inlineStr"/>
       <c r="F150" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G150" s="36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H150" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I150" s="32" t="inlineStr">
@@ -10832,31 +10836,39 @@
     </row>
     <row r="151">
       <c r="A151" s="38" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B151" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C151" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
-        </is>
-      </c>
-      <c r="D151" s="31" t="inlineStr"/>
-      <c r="E151" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D151" s="31" t="inlineStr">
+        <is>
+          <t>Padaria do Sol Ltda</t>
+        </is>
+      </c>
+      <c r="E151" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-01</t>
+        </is>
+      </c>
       <c r="F151" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G151" s="36" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H151" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I151" s="32" t="inlineStr">
@@ -10884,26 +10896,26 @@
       </c>
       <c r="C152" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D152" s="31" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="E152" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-01</t>
+          <t>2521428-61.2026.8.26.0600</t>
         </is>
       </c>
       <c r="F152" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G152" s="36" t="n">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="H152" s="32" t="inlineStr">
         <is>
@@ -10926,7 +10938,7 @@
     </row>
     <row r="153">
       <c r="A153" s="38" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B153" s="32" t="inlineStr">
         <is>
@@ -10940,21 +10952,21 @@
       </c>
       <c r="D153" s="31" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="E153" s="31" t="inlineStr">
         <is>
-          <t>2521428-61.2026.8.26.0600</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="F153" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G153" s="36" t="n">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="H153" s="32" t="inlineStr">
         <is>
@@ -10981,35 +10993,27 @@
       </c>
       <c r="B154" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C154" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D154" s="31" t="inlineStr">
-        <is>
-          <t>Marcos Vinícius Teles</t>
-        </is>
-      </c>
-      <c r="E154" s="31" t="inlineStr">
-        <is>
-          <t>9605863-76.2026.8.26.0026</t>
-        </is>
-      </c>
+          <t>Sistemas e assinaturas</t>
+        </is>
+      </c>
+      <c r="D154" s="31" t="inlineStr"/>
+      <c r="E154" s="31" t="inlineStr"/>
       <c r="F154" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G154" s="36" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="H154" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I154" s="32" t="inlineStr">
@@ -11028,7 +11032,7 @@
     </row>
     <row r="155">
       <c r="A155" s="38" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B155" s="32" t="inlineStr">
         <is>
@@ -11037,22 +11041,22 @@
       </c>
       <c r="C155" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Contador</t>
         </is>
       </c>
       <c r="D155" s="31" t="inlineStr"/>
       <c r="E155" s="31" t="inlineStr"/>
       <c r="F155" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G155" s="36" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="H155" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I155" s="32" t="inlineStr">
@@ -11080,22 +11084,22 @@
       </c>
       <c r="C156" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
+          <t>Pró-labore dos sócios</t>
         </is>
       </c>
       <c r="D156" s="31" t="inlineStr"/>
       <c r="E156" s="31" t="inlineStr"/>
       <c r="F156" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Distribuição de lucro · 2º trimestre · Marina Ferraz</t>
         </is>
       </c>
       <c r="G156" s="36" t="n">
-        <v>600</v>
+        <v>3797</v>
       </c>
       <c r="H156" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I156" s="32" t="inlineStr">
@@ -11130,7 +11134,7 @@
       <c r="E157" s="31" t="inlineStr"/>
       <c r="F157" s="31" t="inlineStr">
         <is>
-          <t>Distribuição de lucro · 2º trimestre · Marina Ferraz</t>
+          <t>Distribuição de lucro · 2º trimestre · Rafael Lima</t>
         </is>
       </c>
       <c r="G157" s="36" t="n">
@@ -11157,7 +11161,7 @@
     </row>
     <row r="158">
       <c r="A158" s="38" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B158" s="32" t="inlineStr">
         <is>
@@ -11166,22 +11170,22 @@
       </c>
       <c r="C158" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
+          <t>Outras saídas</t>
         </is>
       </c>
       <c r="D158" s="31" t="inlineStr"/>
       <c r="E158" s="31" t="inlineStr"/>
       <c r="F158" s="31" t="inlineStr">
         <is>
-          <t>Distribuição de lucro · 2º trimestre · Rafael Lima</t>
+          <t>Despesa pessoal · Rafael Lima · combustível particular (a acertar)</t>
         </is>
       </c>
       <c r="G158" s="36" t="n">
-        <v>3797</v>
+        <v>300</v>
       </c>
       <c r="H158" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I158" s="32" t="inlineStr">
@@ -11200,7 +11204,7 @@
     </row>
     <row r="159">
       <c r="A159" s="38" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B159" s="32" t="inlineStr">
         <is>
@@ -11209,22 +11213,22 @@
       </c>
       <c r="C159" s="31" t="inlineStr">
         <is>
-          <t>Outras saídas</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="D159" s="31" t="inlineStr"/>
       <c r="E159" s="31" t="inlineStr"/>
       <c r="F159" s="31" t="inlineStr">
         <is>
-          <t>Despesa pessoal · Rafael Lima · combustível particular (a acertar)</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G159" s="36" t="n">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="H159" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I159" s="32" t="inlineStr">
@@ -11243,7 +11247,7 @@
     </row>
     <row r="160">
       <c r="A160" s="38" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B160" s="32" t="inlineStr">
         <is>
@@ -11252,18 +11256,26 @@
       </c>
       <c r="C160" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
-        </is>
-      </c>
-      <c r="D160" s="31" t="inlineStr"/>
-      <c r="E160" s="31" t="inlineStr"/>
+          <t>Custas e despesas de processo</t>
+        </is>
+      </c>
+      <c r="D160" s="31" t="inlineStr">
+        <is>
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="E160" s="31" t="inlineStr">
+        <is>
+          <t>2354318-24.2026.8.26.0295</t>
+        </is>
+      </c>
       <c r="F160" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Custas de recurso</t>
         </is>
       </c>
       <c r="G160" s="36" t="n">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="H160" s="32" t="inlineStr">
         <is>
@@ -11286,35 +11298,35 @@
     </row>
     <row r="161">
       <c r="A161" s="38" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B161" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C161" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
+          <t>Consultoria e pareceres</t>
         </is>
       </c>
       <c r="D161" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="E161" s="31" t="inlineStr">
         <is>
-          <t>2354318-24.2026.8.26.0295</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="F161" s="31" t="inlineStr">
         <is>
-          <t>Custas de recurso</t>
+          <t>Fatura de horas · 8</t>
         </is>
       </c>
       <c r="G161" s="36" t="n">
-        <v>310</v>
+        <v>1980</v>
       </c>
       <c r="H161" s="32" t="inlineStr">
         <is>
@@ -11337,7 +11349,7 @@
     </row>
     <row r="162">
       <c r="A162" s="38" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B162" s="32" t="inlineStr">
         <is>
@@ -11346,26 +11358,26 @@
       </c>
       <c r="C162" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D162" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E162" s="31" t="inlineStr">
         <is>
-          <t>CONS-2025-05</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F162" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 8</t>
+          <t>Fatura de horas · 7</t>
         </is>
       </c>
       <c r="G162" s="36" t="n">
-        <v>1980</v>
+        <v>2340</v>
       </c>
       <c r="H162" s="32" t="inlineStr">
         <is>
@@ -11397,7 +11409,7 @@
       </c>
       <c r="C163" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
+          <t>Reembolso de custas</t>
         </is>
       </c>
       <c r="D163" s="31" t="inlineStr">
@@ -11412,15 +11424,15 @@
       </c>
       <c r="F163" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 7</t>
+          <t>Reembolso das custas de recurso</t>
         </is>
       </c>
       <c r="G163" s="36" t="n">
-        <v>2340</v>
+        <v>540</v>
       </c>
       <c r="H163" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I163" s="32" t="inlineStr">
@@ -11443,35 +11455,27 @@
       </c>
       <c r="B164" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C164" s="31" t="inlineStr">
         <is>
-          <t>Reembolso de custas</t>
-        </is>
-      </c>
-      <c r="D164" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E164" s="31" t="inlineStr">
-        <is>
-          <t>9362688-24.2025.8.26.0436</t>
-        </is>
-      </c>
+          <t>Anuidades OAB e cursos</t>
+        </is>
+      </c>
+      <c r="D164" s="31" t="inlineStr"/>
+      <c r="E164" s="31" t="inlineStr"/>
       <c r="F164" s="31" t="inlineStr">
         <is>
-          <t>Reembolso das custas de recurso</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G164" s="36" t="n">
-        <v>540</v>
+        <v>250</v>
       </c>
       <c r="H164" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I164" s="32" t="inlineStr">
@@ -11490,31 +11494,39 @@
     </row>
     <row r="165">
       <c r="A165" s="38" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B165" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C165" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
-        </is>
-      </c>
-      <c r="D165" s="31" t="inlineStr"/>
-      <c r="E165" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D165" s="31" t="inlineStr">
+        <is>
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="E165" s="31" t="inlineStr">
+        <is>
+          <t>2354318-24.2026.8.26.0295</t>
+        </is>
+      </c>
       <c r="F165" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G165" s="36" t="n">
-        <v>250</v>
+        <v>2100</v>
       </c>
       <c r="H165" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I165" s="32" t="inlineStr">
@@ -11533,39 +11545,31 @@
     </row>
     <row r="166">
       <c r="A166" s="38" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B166" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C166" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D166" s="31" t="inlineStr">
-        <is>
-          <t>Roberto Almeida</t>
-        </is>
-      </c>
-      <c r="E166" s="31" t="inlineStr">
-        <is>
-          <t>2354318-24.2026.8.26.0295</t>
-        </is>
-      </c>
+          <t>Material, correio e outros</t>
+        </is>
+      </c>
+      <c r="D166" s="31" t="inlineStr"/>
+      <c r="E166" s="31" t="inlineStr"/>
       <c r="F166" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G166" s="36" t="n">
-        <v>2100</v>
+        <v>380</v>
       </c>
       <c r="H166" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I166" s="32" t="inlineStr">
@@ -11584,31 +11588,39 @@
     </row>
     <row r="167">
       <c r="A167" s="38" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B167" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C167" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D167" s="31" t="inlineStr"/>
-      <c r="E167" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D167" s="31" t="inlineStr">
+        <is>
+          <t>Transportadora Rota Sul</t>
+        </is>
+      </c>
+      <c r="E167" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-06</t>
+        </is>
+      </c>
       <c r="F167" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G167" s="36" t="n">
-        <v>380</v>
+        <v>2200</v>
       </c>
       <c r="H167" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I167" s="32" t="inlineStr">
@@ -11636,17 +11648,17 @@
       </c>
       <c r="C168" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D168" s="31" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="E168" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-06</t>
+          <t>9616569-91.2026.8.26.0079</t>
         </is>
       </c>
       <c r="F168" s="31" t="inlineStr">
@@ -11655,7 +11667,7 @@
         </is>
       </c>
       <c r="G168" s="36" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="H168" s="32" t="inlineStr">
         <is>
@@ -11682,35 +11694,27 @@
       </c>
       <c r="B169" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C169" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D169" s="31" t="inlineStr">
-        <is>
-          <t>Patrícia Gomes</t>
-        </is>
-      </c>
-      <c r="E169" s="31" t="inlineStr">
-        <is>
-          <t>9616569-91.2026.8.26.0079</t>
-        </is>
-      </c>
+          <t>Impostos e taxas</t>
+        </is>
+      </c>
+      <c r="D169" s="31" t="inlineStr"/>
+      <c r="E169" s="31" t="inlineStr"/>
       <c r="F169" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G169" s="36" t="n">
-        <v>2100</v>
+        <v>2194</v>
       </c>
       <c r="H169" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I169" s="32" t="inlineStr">
@@ -11738,22 +11742,22 @@
       </c>
       <c r="C170" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D170" s="31" t="inlineStr"/>
       <c r="E170" s="31" t="inlineStr"/>
       <c r="F170" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G170" s="36" t="n">
-        <v>2194</v>
+        <v>400</v>
       </c>
       <c r="H170" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I170" s="32" t="inlineStr">
@@ -11772,7 +11776,7 @@
     </row>
     <row r="171">
       <c r="A171" s="38" t="n">
-        <v>46223</v>
+        <v>46231</v>
       </c>
       <c r="B171" s="32" t="inlineStr">
         <is>
@@ -11781,22 +11785,22 @@
       </c>
       <c r="C171" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Pró-labore dos sócios</t>
         </is>
       </c>
       <c r="D171" s="31" t="inlineStr"/>
       <c r="E171" s="31" t="inlineStr"/>
       <c r="F171" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G171" s="36" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="H171" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I171" s="32" t="inlineStr">
@@ -11831,7 +11835,7 @@
       <c r="E172" s="31" t="inlineStr"/>
       <c r="F172" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G172" s="36" t="n">
@@ -11858,31 +11862,39 @@
     </row>
     <row r="173">
       <c r="A173" s="38" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B173" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C173" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D173" s="31" t="inlineStr"/>
-      <c r="E173" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D173" s="31" t="inlineStr">
+        <is>
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="E173" s="31" t="inlineStr">
+        <is>
+          <t>9586960-92.2026.8.26.0106</t>
+        </is>
+      </c>
       <c r="F173" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G173" s="36" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="H173" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I173" s="32" t="inlineStr">
@@ -11915,21 +11927,21 @@
       </c>
       <c r="D174" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="E174" s="31" t="inlineStr">
         <is>
-          <t>9586960-92.2026.8.26.0106</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="F174" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G174" s="36" t="n">
-        <v>4200</v>
+        <v>1500</v>
       </c>
       <c r="H174" s="32" t="inlineStr">
         <is>
@@ -11952,7 +11964,7 @@
     </row>
     <row r="175">
       <c r="A175" s="38" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B175" s="32" t="inlineStr">
         <is>
@@ -11966,21 +11978,21 @@
       </c>
       <c r="D175" s="31" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="E175" s="31" t="inlineStr">
         <is>
-          <t>7679821-77.2026.8.26.0265</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="F175" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G175" s="36" t="n">
-        <v>1500</v>
+        <v>2700</v>
       </c>
       <c r="H175" s="32" t="inlineStr">
         <is>
@@ -12003,7 +12015,7 @@
     </row>
     <row r="176">
       <c r="A176" s="38" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B176" s="32" t="inlineStr">
         <is>
@@ -12017,21 +12029,21 @@
       </c>
       <c r="D176" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Carlos Eduardo Nunes</t>
         </is>
       </c>
       <c r="E176" s="31" t="inlineStr">
         <is>
-          <t>2645033-67.2026.8.26.0012</t>
+          <t>4746093-86.2026.8.26.0637</t>
         </is>
       </c>
       <c r="F176" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Honorários · entrada</t>
         </is>
       </c>
       <c r="G176" s="36" t="n">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="H176" s="32" t="inlineStr">
         <is>
@@ -12054,7 +12066,7 @@
     </row>
     <row r="177">
       <c r="A177" s="38" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B177" s="32" t="inlineStr">
         <is>
@@ -12063,26 +12075,26 @@
       </c>
       <c r="C177" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Consultoria e pareceres</t>
         </is>
       </c>
       <c r="D177" s="31" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Padaria do Sol Ltda</t>
         </is>
       </c>
       <c r="E177" s="31" t="inlineStr">
         <is>
-          <t>4746093-86.2026.8.26.0637</t>
+          <t>CONS-2026-01</t>
         </is>
       </c>
       <c r="F177" s="31" t="inlineStr">
         <is>
-          <t>Honorários · entrada</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G177" s="36" t="n">
-        <v>2400</v>
+        <v>1500</v>
       </c>
       <c r="H177" s="32" t="inlineStr">
         <is>
@@ -12096,7 +12108,7 @@
       </c>
       <c r="J177" s="35">
         <f>IF(A177="","",MONTH(A177))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K177" s="35">
         <f>IF(A177="","",YEAR(A177))</f>
@@ -12114,26 +12126,26 @@
       </c>
       <c r="C178" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D178" s="31" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="E178" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-01</t>
+          <t>2521428-61.2026.8.26.0600</t>
         </is>
       </c>
       <c r="F178" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G178" s="36" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="H178" s="32" t="inlineStr">
         <is>
@@ -12160,35 +12172,27 @@
       </c>
       <c r="B179" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C179" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D179" s="31" t="inlineStr">
-        <is>
-          <t>Luciana Farias</t>
-        </is>
-      </c>
-      <c r="E179" s="31" t="inlineStr">
-        <is>
-          <t>2521428-61.2026.8.26.0600</t>
-        </is>
-      </c>
+          <t>Aluguel e condomínio</t>
+        </is>
+      </c>
+      <c r="D179" s="31" t="inlineStr"/>
+      <c r="E179" s="31" t="inlineStr"/>
       <c r="F179" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G179" s="36" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="H179" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I179" s="32" t="inlineStr">
@@ -12216,18 +12220,26 @@
       </c>
       <c r="C180" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
-        </is>
-      </c>
-      <c r="D180" s="31" t="inlineStr"/>
-      <c r="E180" s="31" t="inlineStr"/>
+          <t>Custas e despesas de processo</t>
+        </is>
+      </c>
+      <c r="D180" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="E180" s="31" t="inlineStr">
+        <is>
+          <t>9616569-91.2026.8.26.0079</t>
+        </is>
+      </c>
       <c r="F180" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Custas de execução</t>
         </is>
       </c>
       <c r="G180" s="36" t="n">
-        <v>2800</v>
+        <v>380</v>
       </c>
       <c r="H180" s="32" t="inlineStr">
         <is>
@@ -12259,30 +12271,22 @@
       </c>
       <c r="C181" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
-        </is>
-      </c>
-      <c r="D181" s="31" t="inlineStr">
-        <is>
-          <t>Patrícia Gomes</t>
-        </is>
-      </c>
-      <c r="E181" s="31" t="inlineStr">
-        <is>
-          <t>9616569-91.2026.8.26.0079</t>
-        </is>
-      </c>
+          <t>Estagiária (bolsa)</t>
+        </is>
+      </c>
+      <c r="D181" s="31" t="inlineStr"/>
+      <c r="E181" s="31" t="inlineStr"/>
       <c r="F181" s="31" t="inlineStr">
         <is>
-          <t>Custas de execução</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G181" s="36" t="n">
-        <v>380</v>
+        <v>1400</v>
       </c>
       <c r="H181" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I181" s="32" t="inlineStr">
@@ -12301,7 +12305,7 @@
     </row>
     <row r="182">
       <c r="A182" s="38" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B182" s="32" t="inlineStr">
         <is>
@@ -12310,22 +12314,22 @@
       </c>
       <c r="C182" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
+          <t>Outras saídas</t>
         </is>
       </c>
       <c r="D182" s="31" t="inlineStr"/>
       <c r="E182" s="31" t="inlineStr"/>
       <c r="F182" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Despesa pessoal · Marina Ferraz · plano de saúde particular (a acertar)</t>
         </is>
       </c>
       <c r="G182" s="36" t="n">
-        <v>1400</v>
+        <v>480</v>
       </c>
       <c r="H182" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I182" s="32" t="inlineStr">
@@ -12344,31 +12348,39 @@
     </row>
     <row r="183">
       <c r="A183" s="38" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B183" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C183" s="31" t="inlineStr">
         <is>
-          <t>Outras saídas</t>
-        </is>
-      </c>
-      <c r="D183" s="31" t="inlineStr"/>
-      <c r="E183" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D183" s="31" t="inlineStr">
+        <is>
+          <t>Luciana Farias</t>
+        </is>
+      </c>
+      <c r="E183" s="31" t="inlineStr">
+        <is>
+          <t>7099226-69.2026.8.26.0433</t>
+        </is>
+      </c>
       <c r="F183" s="31" t="inlineStr">
         <is>
-          <t>Despesa pessoal · Marina Ferraz · plano de saúde particular (a acertar)</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G183" s="36" t="n">
-        <v>480</v>
+        <v>2500</v>
       </c>
       <c r="H183" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I183" s="32" t="inlineStr">
@@ -12401,12 +12413,12 @@
       </c>
       <c r="D184" s="31" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="E184" s="31" t="inlineStr">
         <is>
-          <t>7099226-69.2026.8.26.0433</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="F184" s="31" t="inlineStr">
@@ -12415,7 +12427,7 @@
         </is>
       </c>
       <c r="G184" s="36" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="H184" s="32" t="inlineStr">
         <is>
@@ -12438,39 +12450,31 @@
     </row>
     <row r="185">
       <c r="A185" s="38" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B185" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C185" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D185" s="31" t="inlineStr">
-        <is>
-          <t>Marcos Vinícius Teles</t>
-        </is>
-      </c>
-      <c r="E185" s="31" t="inlineStr">
-        <is>
-          <t>9605863-76.2026.8.26.0026</t>
-        </is>
-      </c>
+          <t>Sistemas e assinaturas</t>
+        </is>
+      </c>
+      <c r="D185" s="31" t="inlineStr"/>
+      <c r="E185" s="31" t="inlineStr"/>
       <c r="F185" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G185" s="36" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="H185" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I185" s="32" t="inlineStr">
@@ -12489,31 +12493,39 @@
     </row>
     <row r="186">
       <c r="A186" s="38" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B186" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C186" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
-        </is>
-      </c>
-      <c r="D186" s="31" t="inlineStr"/>
-      <c r="E186" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D186" s="31" t="inlineStr">
+        <is>
+          <t>Escola Aurora</t>
+        </is>
+      </c>
+      <c r="E186" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-04</t>
+        </is>
+      </c>
       <c r="F186" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G186" s="36" t="n">
-        <v>450</v>
+        <v>1100</v>
       </c>
       <c r="H186" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I186" s="32" t="inlineStr">
@@ -12546,25 +12558,25 @@
       </c>
       <c r="D187" s="31" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="E187" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-04</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="F187" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Fatura de horas · 9</t>
         </is>
       </c>
       <c r="G187" s="36" t="n">
-        <v>1100</v>
+        <v>1440</v>
       </c>
       <c r="H187" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I187" s="32" t="inlineStr">
@@ -12592,30 +12604,30 @@
       </c>
       <c r="C188" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D188" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="E188" s="31" t="inlineStr">
         <is>
-          <t>CONS-2025-05</t>
+          <t>6832730-55.2026.8.26.0386</t>
         </is>
       </c>
       <c r="F188" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 9</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G188" s="36" t="n">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="H188" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I188" s="32" t="inlineStr">
@@ -12643,22 +12655,22 @@
       </c>
       <c r="C189" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D189" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E189" s="31" t="inlineStr">
         <is>
-          <t>6832730-55.2026.8.26.0386</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F189" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Fatura de horas · 8 (vencida)</t>
         </is>
       </c>
       <c r="G189" s="36" t="n">
@@ -12666,12 +12678,12 @@
       </c>
       <c r="H189" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I189" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J189" s="35">
@@ -12689,31 +12701,23 @@
       </c>
       <c r="B190" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C190" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
-        </is>
-      </c>
-      <c r="D190" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E190" s="31" t="inlineStr">
-        <is>
-          <t>9362688-24.2025.8.26.0436</t>
-        </is>
-      </c>
+          <t>Contador</t>
+        </is>
+      </c>
+      <c r="D190" s="31" t="inlineStr"/>
+      <c r="E190" s="31" t="inlineStr"/>
       <c r="F190" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 8 (vencida)</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G190" s="36" t="n">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="H190" s="32" t="inlineStr">
         <is>
@@ -12722,7 +12726,7 @@
       </c>
       <c r="I190" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J190" s="35">
@@ -12736,31 +12740,39 @@
     </row>
     <row r="191">
       <c r="A191" s="38" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B191" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C191" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
-        </is>
-      </c>
-      <c r="D191" s="31" t="inlineStr"/>
-      <c r="E191" s="31" t="inlineStr"/>
+          <t>Reembolso de custas</t>
+        </is>
+      </c>
+      <c r="D191" s="31" t="inlineStr">
+        <is>
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="E191" s="31" t="inlineStr">
+        <is>
+          <t>2354318-24.2026.8.26.0295</t>
+        </is>
+      </c>
       <c r="F191" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Reembolso das custas de recurso</t>
         </is>
       </c>
       <c r="G191" s="36" t="n">
-        <v>600</v>
+        <v>310</v>
       </c>
       <c r="H191" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I191" s="32" t="inlineStr">
@@ -12783,35 +12795,27 @@
       </c>
       <c r="B192" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C192" s="31" t="inlineStr">
         <is>
-          <t>Reembolso de custas</t>
-        </is>
-      </c>
-      <c r="D192" s="31" t="inlineStr">
-        <is>
-          <t>Roberto Almeida</t>
-        </is>
-      </c>
-      <c r="E192" s="31" t="inlineStr">
-        <is>
-          <t>2354318-24.2026.8.26.0295</t>
-        </is>
-      </c>
+          <t>Telefone e internet</t>
+        </is>
+      </c>
+      <c r="D192" s="31" t="inlineStr"/>
+      <c r="E192" s="31" t="inlineStr"/>
       <c r="F192" s="31" t="inlineStr">
         <is>
-          <t>Reembolso das custas de recurso</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G192" s="36" t="n">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="H192" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I192" s="32" t="inlineStr">
@@ -12830,27 +12834,35 @@
     </row>
     <row r="193">
       <c r="A193" s="38" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B193" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C193" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
-        </is>
-      </c>
-      <c r="D193" s="31" t="inlineStr"/>
-      <c r="E193" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D193" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="E193" s="31" t="inlineStr">
+        <is>
+          <t>9616569-91.2026.8.26.0079</t>
+        </is>
+      </c>
       <c r="F193" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Honorários · parcela 2 (vencida)</t>
         </is>
       </c>
       <c r="G193" s="36" t="n">
-        <v>220</v>
+        <v>2100</v>
       </c>
       <c r="H193" s="32" t="inlineStr">
         <is>
@@ -12859,7 +12871,7 @@
       </c>
       <c r="I193" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J193" s="35">
@@ -12873,44 +12885,36 @@
     </row>
     <row r="194">
       <c r="A194" s="38" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B194" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C194" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D194" s="31" t="inlineStr">
-        <is>
-          <t>Patrícia Gomes</t>
-        </is>
-      </c>
-      <c r="E194" s="31" t="inlineStr">
-        <is>
-          <t>9616569-91.2026.8.26.0079</t>
-        </is>
-      </c>
+          <t>Anuidades OAB e cursos</t>
+        </is>
+      </c>
+      <c r="D194" s="31" t="inlineStr"/>
+      <c r="E194" s="31" t="inlineStr"/>
       <c r="F194" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2 (vencida)</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G194" s="36" t="n">
-        <v>2100</v>
+        <v>250</v>
       </c>
       <c r="H194" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I194" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J194" s="35">
@@ -12924,31 +12928,39 @@
     </row>
     <row r="195">
       <c r="A195" s="38" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="B195" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C195" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
-        </is>
-      </c>
-      <c r="D195" s="31" t="inlineStr"/>
-      <c r="E195" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D195" s="31" t="inlineStr">
+        <is>
+          <t>Loja Verde Comércio</t>
+        </is>
+      </c>
+      <c r="E195" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-02</t>
+        </is>
+      </c>
       <c r="F195" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G195" s="36" t="n">
-        <v>250</v>
+        <v>2800</v>
       </c>
       <c r="H195" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I195" s="32" t="inlineStr">
@@ -12971,35 +12983,27 @@
       </c>
       <c r="B196" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C196" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
-        </is>
-      </c>
-      <c r="D196" s="31" t="inlineStr">
-        <is>
-          <t>Loja Verde Comércio</t>
-        </is>
-      </c>
-      <c r="E196" s="31" t="inlineStr">
-        <is>
-          <t>CONS-2026-02</t>
-        </is>
-      </c>
+          <t>Material, correio e outros</t>
+        </is>
+      </c>
+      <c r="D196" s="31" t="inlineStr"/>
+      <c r="E196" s="31" t="inlineStr"/>
       <c r="F196" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G196" s="36" t="n">
-        <v>2800</v>
+        <v>380</v>
       </c>
       <c r="H196" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I196" s="32" t="inlineStr">
@@ -13018,31 +13022,39 @@
     </row>
     <row r="197">
       <c r="A197" s="38" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B197" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C197" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
-        </is>
-      </c>
-      <c r="D197" s="31" t="inlineStr"/>
-      <c r="E197" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D197" s="31" t="inlineStr">
+        <is>
+          <t>Transportadora Rota Sul</t>
+        </is>
+      </c>
+      <c r="E197" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-06</t>
+        </is>
+      </c>
       <c r="F197" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G197" s="36" t="n">
-        <v>380</v>
+        <v>2200</v>
       </c>
       <c r="H197" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I197" s="32" t="inlineStr">
@@ -13065,35 +13077,27 @@
       </c>
       <c r="B198" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C198" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
-        </is>
-      </c>
-      <c r="D198" s="31" t="inlineStr">
-        <is>
-          <t>Transportadora Rota Sul</t>
-        </is>
-      </c>
-      <c r="E198" s="31" t="inlineStr">
-        <is>
-          <t>CONS-2026-06</t>
-        </is>
-      </c>
+          <t>Deslocamento e viagens</t>
+        </is>
+      </c>
+      <c r="D198" s="31" t="inlineStr"/>
+      <c r="E198" s="31" t="inlineStr"/>
       <c r="F198" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Combustível e estacionamento (audiências)</t>
         </is>
       </c>
       <c r="G198" s="36" t="n">
-        <v>2200</v>
+        <v>180</v>
       </c>
       <c r="H198" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I198" s="32" t="inlineStr">
@@ -13112,7 +13116,7 @@
     </row>
     <row r="199">
       <c r="A199" s="38" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B199" s="32" t="inlineStr">
         <is>
@@ -13121,22 +13125,22 @@
       </c>
       <c r="C199" s="31" t="inlineStr">
         <is>
-          <t>Deslocamento e viagens</t>
+          <t>Impostos e taxas</t>
         </is>
       </c>
       <c r="D199" s="31" t="inlineStr"/>
       <c r="E199" s="31" t="inlineStr"/>
       <c r="F199" s="31" t="inlineStr">
         <is>
-          <t>Combustível e estacionamento (audiências)</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G199" s="36" t="n">
-        <v>180</v>
+        <v>2357</v>
       </c>
       <c r="H199" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I199" s="32" t="inlineStr">
@@ -13164,22 +13168,22 @@
       </c>
       <c r="C200" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D200" s="31" t="inlineStr"/>
       <c r="E200" s="31" t="inlineStr"/>
       <c r="F200" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G200" s="36" t="n">
-        <v>2357</v>
+        <v>400</v>
       </c>
       <c r="H200" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I200" s="32" t="inlineStr">
@@ -13198,31 +13202,39 @@
     </row>
     <row r="201">
       <c r="A201" s="38" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B201" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C201" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
-        </is>
-      </c>
-      <c r="D201" s="31" t="inlineStr"/>
-      <c r="E201" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D201" s="31" t="inlineStr">
+        <is>
+          <t>Marcos Vinícius Teles</t>
+        </is>
+      </c>
+      <c r="E201" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-03</t>
+        </is>
+      </c>
       <c r="F201" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G201" s="36" t="n">
-        <v>400</v>
+        <v>2250</v>
       </c>
       <c r="H201" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I201" s="32" t="inlineStr">
@@ -13241,7 +13253,7 @@
     </row>
     <row r="202">
       <c r="A202" s="38" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B202" s="32" t="inlineStr">
         <is>
@@ -13250,17 +13262,17 @@
       </c>
       <c r="C202" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D202" s="31" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Construtora Horizonte</t>
         </is>
       </c>
       <c r="E202" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-03</t>
+          <t>9586960-92.2026.8.26.0106</t>
         </is>
       </c>
       <c r="F202" s="31" t="inlineStr">
@@ -13269,7 +13281,7 @@
         </is>
       </c>
       <c r="G202" s="36" t="n">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="H202" s="32" t="inlineStr">
         <is>
@@ -13306,21 +13318,21 @@
       </c>
       <c r="D203" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="E203" s="31" t="inlineStr">
         <is>
-          <t>9586960-92.2026.8.26.0106</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="F203" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G203" s="36" t="n">
-        <v>2100</v>
+        <v>2700</v>
       </c>
       <c r="H203" s="32" t="inlineStr">
         <is>
@@ -13357,30 +13369,30 @@
       </c>
       <c r="D204" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="E204" s="31" t="inlineStr">
         <is>
-          <t>2645033-67.2026.8.26.0012</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="F204" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Honorários · parcela 2 (vencida)</t>
         </is>
       </c>
       <c r="G204" s="36" t="n">
-        <v>2700</v>
+        <v>1500</v>
       </c>
       <c r="H204" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I204" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J204" s="35">
@@ -13398,40 +13410,32 @@
       </c>
       <c r="B205" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C205" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D205" s="31" t="inlineStr">
-        <is>
-          <t>Helena Duarte</t>
-        </is>
-      </c>
-      <c r="E205" s="31" t="inlineStr">
-        <is>
-          <t>7679821-77.2026.8.26.0265</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D205" s="31" t="inlineStr"/>
+      <c r="E205" s="31" t="inlineStr"/>
       <c r="F205" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2 (vencida)</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G205" s="36" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="H205" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I205" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J205" s="35">
@@ -13461,7 +13465,7 @@
       <c r="E206" s="31" t="inlineStr"/>
       <c r="F206" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G206" s="36" t="n">
@@ -13488,31 +13492,39 @@
     </row>
     <row r="207">
       <c r="A207" s="38" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B207" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C207" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D207" s="31" t="inlineStr"/>
-      <c r="E207" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D207" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Nunes</t>
+        </is>
+      </c>
+      <c r="E207" s="31" t="inlineStr">
+        <is>
+          <t>4746093-86.2026.8.26.0637</t>
+        </is>
+      </c>
       <c r="F207" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Honorários · parcela 1</t>
         </is>
       </c>
       <c r="G207" s="36" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="H207" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I207" s="32" t="inlineStr">
@@ -13545,21 +13557,21 @@
       </c>
       <c r="D208" s="31" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="E208" s="31" t="inlineStr">
         <is>
-          <t>4746093-86.2026.8.26.0637</t>
+          <t>7099226-69.2026.8.26.0433</t>
         </is>
       </c>
       <c r="F208" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 1</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G208" s="36" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="H208" s="32" t="inlineStr">
         <is>
@@ -13582,39 +13594,39 @@
     </row>
     <row r="209">
       <c r="A209" s="38" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B209" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C209" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Custas e despesas de processo</t>
         </is>
       </c>
       <c r="D209" s="31" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="E209" s="31" t="inlineStr">
         <is>
-          <t>7099226-69.2026.8.26.0433</t>
+          <t>6710873-21.2025.8.26.0571</t>
         </is>
       </c>
       <c r="F209" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Certidões</t>
         </is>
       </c>
       <c r="G209" s="36" t="n">
-        <v>2500</v>
+        <v>70</v>
       </c>
       <c r="H209" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I209" s="32" t="inlineStr">
@@ -13624,7 +13636,7 @@
       </c>
       <c r="J209" s="35">
         <f>IF(A209="","",MONTH(A209))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K209" s="35">
         <f>IF(A209="","",YEAR(A209))</f>
@@ -13633,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="38" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B210" s="32" t="inlineStr">
         <is>
@@ -13642,26 +13654,18 @@
       </c>
       <c r="C210" s="31" t="inlineStr">
         <is>
-          <t>Custas e despesas de processo</t>
-        </is>
-      </c>
-      <c r="D210" s="31" t="inlineStr">
-        <is>
-          <t>Escola Aurora</t>
-        </is>
-      </c>
-      <c r="E210" s="31" t="inlineStr">
-        <is>
-          <t>6710873-21.2025.8.26.0571</t>
-        </is>
-      </c>
+          <t>Aluguel e condomínio</t>
+        </is>
+      </c>
+      <c r="D210" s="31" t="inlineStr"/>
+      <c r="E210" s="31" t="inlineStr"/>
       <c r="F210" s="31" t="inlineStr">
         <is>
-          <t>Certidões</t>
+          <t>Aluguel e condomínio da sala</t>
         </is>
       </c>
       <c r="G210" s="36" t="n">
-        <v>70</v>
+        <v>2800</v>
       </c>
       <c r="H210" s="32" t="inlineStr">
         <is>
@@ -13693,22 +13697,22 @@
       </c>
       <c r="C211" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio</t>
+          <t>Estagiária (bolsa)</t>
         </is>
       </c>
       <c r="D211" s="31" t="inlineStr"/>
       <c r="E211" s="31" t="inlineStr"/>
       <c r="F211" s="31" t="inlineStr">
         <is>
-          <t>Aluguel e condomínio da sala</t>
+          <t>Bolsa da estagiária · Júlia Prado</t>
         </is>
       </c>
       <c r="G211" s="36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H211" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I211" s="32" t="inlineStr">
@@ -13727,31 +13731,39 @@
     </row>
     <row r="212">
       <c r="A212" s="38" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B212" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C212" s="31" t="inlineStr">
         <is>
-          <t>Estagiária (bolsa)</t>
-        </is>
-      </c>
-      <c r="D212" s="31" t="inlineStr"/>
-      <c r="E212" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D212" s="31" t="inlineStr">
+        <is>
+          <t>Padaria do Sol Ltda</t>
+        </is>
+      </c>
+      <c r="E212" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-01</t>
+        </is>
+      </c>
       <c r="F212" s="31" t="inlineStr">
         <is>
-          <t>Bolsa da estagiária · Júlia Prado</t>
+          <t>Honorários · parcela 3</t>
         </is>
       </c>
       <c r="G212" s="36" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H212" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I212" s="32" t="inlineStr">
@@ -13779,17 +13791,17 @@
       </c>
       <c r="C213" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D213" s="31" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="E213" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-01</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="F213" s="31" t="inlineStr">
@@ -13798,7 +13810,7 @@
         </is>
       </c>
       <c r="G213" s="36" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="H213" s="32" t="inlineStr">
         <is>
@@ -13825,35 +13837,27 @@
       </c>
       <c r="B214" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C214" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D214" s="31" t="inlineStr">
-        <is>
-          <t>Marcos Vinícius Teles</t>
-        </is>
-      </c>
-      <c r="E214" s="31" t="inlineStr">
-        <is>
-          <t>9605863-76.2026.8.26.0026</t>
-        </is>
-      </c>
+          <t>Sistemas e assinaturas</t>
+        </is>
+      </c>
+      <c r="D214" s="31" t="inlineStr"/>
+      <c r="E214" s="31" t="inlineStr"/>
       <c r="F214" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3</t>
+          <t>Sistemas e assinaturas</t>
         </is>
       </c>
       <c r="G214" s="36" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="H214" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I214" s="32" t="inlineStr">
@@ -13872,31 +13876,39 @@
     </row>
     <row r="215">
       <c r="A215" s="38" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B215" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C215" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
-        </is>
-      </c>
-      <c r="D215" s="31" t="inlineStr"/>
-      <c r="E215" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D215" s="31" t="inlineStr">
+        <is>
+          <t>Escola Aurora</t>
+        </is>
+      </c>
+      <c r="E215" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-04</t>
+        </is>
+      </c>
       <c r="F215" s="31" t="inlineStr">
         <is>
-          <t>Sistemas e assinaturas</t>
+          <t>Honorários · parcela 2</t>
         </is>
       </c>
       <c r="G215" s="36" t="n">
-        <v>450</v>
+        <v>1100</v>
       </c>
       <c r="H215" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="I215" s="32" t="inlineStr">
@@ -13924,35 +13936,35 @@
       </c>
       <c r="C216" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários por hora</t>
         </is>
       </c>
       <c r="D216" s="31" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="E216" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-04</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="F216" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2</t>
+          <t>Fatura de horas · 9 (vencida)</t>
         </is>
       </c>
       <c r="G216" s="36" t="n">
-        <v>1100</v>
+        <v>1980</v>
       </c>
       <c r="H216" s="32" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I216" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J216" s="35">
@@ -13970,31 +13982,23 @@
       </c>
       <c r="B217" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C217" s="31" t="inlineStr">
         <is>
-          <t>Honorários por hora</t>
-        </is>
-      </c>
-      <c r="D217" s="31" t="inlineStr">
-        <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="E217" s="31" t="inlineStr">
-        <is>
-          <t>9362688-24.2025.8.26.0436</t>
-        </is>
-      </c>
+          <t>Contador</t>
+        </is>
+      </c>
+      <c r="D217" s="31" t="inlineStr"/>
+      <c r="E217" s="31" t="inlineStr"/>
       <c r="F217" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 9 (vencida)</t>
+          <t>Honorários do contador</t>
         </is>
       </c>
       <c r="G217" s="36" t="n">
-        <v>1980</v>
+        <v>600</v>
       </c>
       <c r="H217" s="32" t="inlineStr">
         <is>
@@ -14003,7 +14007,7 @@
       </c>
       <c r="I217" s="32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J217" s="35">
@@ -14017,27 +14021,35 @@
     </row>
     <row r="218">
       <c r="A218" s="38" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B218" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C218" s="31" t="inlineStr">
         <is>
-          <t>Contador</t>
-        </is>
-      </c>
-      <c r="D218" s="31" t="inlineStr"/>
-      <c r="E218" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D218" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="E218" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2025-05</t>
+        </is>
+      </c>
       <c r="F218" s="31" t="inlineStr">
         <is>
-          <t>Honorários do contador</t>
+          <t>Fatura de horas · 10</t>
         </is>
       </c>
       <c r="G218" s="36" t="n">
-        <v>600</v>
+        <v>1620</v>
       </c>
       <c r="H218" s="32" t="inlineStr">
         <is>
@@ -14060,35 +14072,27 @@
     </row>
     <row r="219">
       <c r="A219" s="38" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B219" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C219" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
-        </is>
-      </c>
-      <c r="D219" s="31" t="inlineStr">
-        <is>
-          <t>Clínica Bem-Estar</t>
-        </is>
-      </c>
-      <c r="E219" s="31" t="inlineStr">
-        <is>
-          <t>CONS-2025-05</t>
-        </is>
-      </c>
+          <t>Telefone e internet</t>
+        </is>
+      </c>
+      <c r="D219" s="31" t="inlineStr"/>
+      <c r="E219" s="31" t="inlineStr"/>
       <c r="F219" s="31" t="inlineStr">
         <is>
-          <t>Fatura de horas · 10</t>
+          <t>Telefone e internet</t>
         </is>
       </c>
       <c r="G219" s="36" t="n">
-        <v>1620</v>
+        <v>220</v>
       </c>
       <c r="H219" s="32" t="inlineStr">
         <is>
@@ -14097,7 +14101,7 @@
       </c>
       <c r="I219" s="32" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="J219" s="35">
@@ -14111,7 +14115,7 @@
     </row>
     <row r="220">
       <c r="A220" s="38" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B220" s="32" t="inlineStr">
         <is>
@@ -14120,22 +14124,22 @@
       </c>
       <c r="C220" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="D220" s="31" t="inlineStr"/>
       <c r="E220" s="31" t="inlineStr"/>
       <c r="F220" s="31" t="inlineStr">
         <is>
-          <t>Telefone e internet</t>
+          <t>Anuidades OAB e cursos</t>
         </is>
       </c>
       <c r="G220" s="36" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="H220" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I220" s="32" t="inlineStr">
@@ -14154,31 +14158,39 @@
     </row>
     <row r="221">
       <c r="A221" s="38" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B221" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C221" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
-        </is>
-      </c>
-      <c r="D221" s="31" t="inlineStr"/>
-      <c r="E221" s="31" t="inlineStr"/>
+          <t>Consultoria e pareceres</t>
+        </is>
+      </c>
+      <c r="D221" s="31" t="inlineStr">
+        <is>
+          <t>Loja Verde Comércio</t>
+        </is>
+      </c>
+      <c r="E221" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2026-02</t>
+        </is>
+      </c>
       <c r="F221" s="31" t="inlineStr">
         <is>
-          <t>Anuidades OAB e cursos</t>
+          <t>Honorários · parcela 2 (a receber)</t>
         </is>
       </c>
       <c r="G221" s="36" t="n">
-        <v>250</v>
+        <v>2800</v>
       </c>
       <c r="H221" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I221" s="32" t="inlineStr">
@@ -14197,39 +14209,31 @@
     </row>
     <row r="222">
       <c r="A222" s="38" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B222" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C222" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
-        </is>
-      </c>
-      <c r="D222" s="31" t="inlineStr">
-        <is>
-          <t>Loja Verde Comércio</t>
-        </is>
-      </c>
-      <c r="E222" s="31" t="inlineStr">
-        <is>
-          <t>CONS-2026-02</t>
-        </is>
-      </c>
+          <t>Material, correio e outros</t>
+        </is>
+      </c>
+      <c r="D222" s="31" t="inlineStr"/>
+      <c r="E222" s="31" t="inlineStr"/>
       <c r="F222" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2 (a receber)</t>
+          <t>Material, correio e outros</t>
         </is>
       </c>
       <c r="G222" s="36" t="n">
-        <v>2800</v>
+        <v>380</v>
       </c>
       <c r="H222" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I222" s="32" t="inlineStr">
@@ -14248,7 +14252,7 @@
     </row>
     <row r="223">
       <c r="A223" s="38" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B223" s="32" t="inlineStr">
         <is>
@@ -14257,22 +14261,22 @@
       </c>
       <c r="C223" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Impostos e taxas</t>
         </is>
       </c>
       <c r="D223" s="31" t="inlineStr"/>
       <c r="E223" s="31" t="inlineStr"/>
       <c r="F223" s="31" t="inlineStr">
         <is>
-          <t>Material, correio e outros</t>
+          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
         </is>
       </c>
       <c r="G223" s="36" t="n">
-        <v>380</v>
+        <v>2152</v>
       </c>
       <c r="H223" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I223" s="32" t="inlineStr">
@@ -14300,22 +14304,22 @@
       </c>
       <c r="C224" s="31" t="inlineStr">
         <is>
-          <t>Impostos e taxas</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="D224" s="31" t="inlineStr"/>
       <c r="E224" s="31" t="inlineStr"/>
       <c r="F224" s="31" t="inlineStr">
         <is>
-          <t>Guia de impostos do mês anterior (alíquota efetiva combinada com o contador)</t>
+          <t>Marketing e site</t>
         </is>
       </c>
       <c r="G224" s="36" t="n">
-        <v>2152</v>
+        <v>400</v>
       </c>
       <c r="H224" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Cartão</t>
         </is>
       </c>
       <c r="I224" s="32" t="inlineStr">
@@ -14334,31 +14338,39 @@
     </row>
     <row r="225">
       <c r="A225" s="38" t="n">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="B225" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C225" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
-        </is>
-      </c>
-      <c r="D225" s="31" t="inlineStr"/>
-      <c r="E225" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D225" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="E225" s="31" t="inlineStr">
+        <is>
+          <t>2645033-67.2026.8.26.0012</t>
+        </is>
+      </c>
       <c r="F225" s="31" t="inlineStr">
         <is>
-          <t>Marketing e site</t>
+          <t>Honorários · parcela 4 (a receber)</t>
         </is>
       </c>
       <c r="G225" s="36" t="n">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="H225" s="32" t="inlineStr">
         <is>
-          <t>Cartão</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I225" s="32" t="inlineStr">
@@ -14377,7 +14389,7 @@
     </row>
     <row r="226">
       <c r="A226" s="38" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B226" s="32" t="inlineStr">
         <is>
@@ -14386,26 +14398,26 @@
       </c>
       <c r="C226" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
+          <t>Consultoria e pareceres</t>
         </is>
       </c>
       <c r="D226" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="E226" s="31" t="inlineStr">
         <is>
-          <t>2645033-67.2026.8.26.0012</t>
+          <t>CONS-2026-03</t>
         </is>
       </c>
       <c r="F226" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 4 (a receber)</t>
+          <t>Honorários · parcela 2 (a receber)</t>
         </is>
       </c>
       <c r="G226" s="36" t="n">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="H226" s="32" t="inlineStr">
         <is>
@@ -14428,7 +14440,7 @@
     </row>
     <row r="227">
       <c r="A227" s="38" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B227" s="32" t="inlineStr">
         <is>
@@ -14437,17 +14449,17 @@
       </c>
       <c r="C227" s="31" t="inlineStr">
         <is>
-          <t>Consultoria e pareceres</t>
+          <t>Honorários fixos</t>
         </is>
       </c>
       <c r="D227" s="31" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Construtora Horizonte</t>
         </is>
       </c>
       <c r="E227" s="31" t="inlineStr">
         <is>
-          <t>CONS-2026-03</t>
+          <t>9586960-92.2026.8.26.0106</t>
         </is>
       </c>
       <c r="F227" s="31" t="inlineStr">
@@ -14456,7 +14468,7 @@
         </is>
       </c>
       <c r="G227" s="36" t="n">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="H227" s="32" t="inlineStr">
         <is>
@@ -14493,21 +14505,21 @@
       </c>
       <c r="D228" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="E228" s="31" t="inlineStr">
         <is>
-          <t>9586960-92.2026.8.26.0106</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="F228" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 2 (a receber)</t>
+          <t>Honorários · parcela 3 (a receber)</t>
         </is>
       </c>
       <c r="G228" s="36" t="n">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="H228" s="32" t="inlineStr">
         <is>
@@ -14534,35 +14546,27 @@
       </c>
       <c r="B229" s="32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="C229" s="31" t="inlineStr">
         <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D229" s="31" t="inlineStr">
-        <is>
-          <t>Helena Duarte</t>
-        </is>
-      </c>
-      <c r="E229" s="31" t="inlineStr">
-        <is>
-          <t>7679821-77.2026.8.26.0265</t>
-        </is>
-      </c>
+          <t>Pró-labore dos sócios</t>
+        </is>
+      </c>
+      <c r="D229" s="31" t="inlineStr"/>
+      <c r="E229" s="31" t="inlineStr"/>
       <c r="F229" s="31" t="inlineStr">
         <is>
-          <t>Honorários · parcela 3 (a receber)</t>
+          <t>Pró-labore · Marina Ferraz</t>
         </is>
       </c>
       <c r="G229" s="36" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="H229" s="32" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Transferência</t>
         </is>
       </c>
       <c r="I229" s="32" t="inlineStr">
@@ -14597,7 +14601,7 @@
       <c r="E230" s="31" t="inlineStr"/>
       <c r="F230" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Marina Ferraz</t>
+          <t>Pró-labore · Rafael Lima</t>
         </is>
       </c>
       <c r="G230" s="36" t="n">
@@ -14624,31 +14628,39 @@
     </row>
     <row r="231">
       <c r="A231" s="38" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B231" s="32" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C231" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore dos sócios</t>
-        </is>
-      </c>
-      <c r="D231" s="31" t="inlineStr"/>
-      <c r="E231" s="31" t="inlineStr"/>
+          <t>Honorários fixos</t>
+        </is>
+      </c>
+      <c r="D231" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Nunes</t>
+        </is>
+      </c>
+      <c r="E231" s="31" t="inlineStr">
+        <is>
+          <t>4746093-86.2026.8.26.0637</t>
+        </is>
+      </c>
       <c r="F231" s="31" t="inlineStr">
         <is>
-          <t>Pró-labore · Rafael Lima</t>
+          <t>Honorários · parcela 2 (a receber)</t>
         </is>
       </c>
       <c r="G231" s="36" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="H231" s="32" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="I231" s="32" t="inlineStr">
@@ -14666,54 +14678,22 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="38" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B232" s="32" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C232" s="31" t="inlineStr">
-        <is>
-          <t>Honorários fixos</t>
-        </is>
-      </c>
-      <c r="D232" s="31" t="inlineStr">
-        <is>
-          <t>Carlos Eduardo Nunes</t>
-        </is>
-      </c>
-      <c r="E232" s="31" t="inlineStr">
-        <is>
-          <t>4746093-86.2026.8.26.0637</t>
-        </is>
-      </c>
-      <c r="F232" s="31" t="inlineStr">
-        <is>
-          <t>Honorários · parcela 2 (a receber)</t>
-        </is>
-      </c>
-      <c r="G232" s="36" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H232" s="32" t="inlineStr">
-        <is>
-          <t>Boleto</t>
-        </is>
-      </c>
-      <c r="I232" s="32" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A232" s="38" t="n"/>
+      <c r="B232" s="32" t="n"/>
+      <c r="C232" s="31" t="n"/>
+      <c r="D232" s="31" t="n"/>
+      <c r="E232" s="31" t="n"/>
+      <c r="F232" s="31" t="n"/>
+      <c r="G232" s="36" t="n"/>
+      <c r="H232" s="32" t="n"/>
+      <c r="I232" s="32" t="n"/>
       <c r="J232" s="35">
         <f>IF(A232="","",MONTH(A232))</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="K232" s="35">
         <f>IF(A232="","",YEAR(A232))</f>
-        <v>2026</v>
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -21803,10 +21783,10 @@
     <dataValidation sqref="B5:B604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Entrada,Saída"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$H$5,0,0,MAX(1,COUNTA(Config!$D$5:$D$16)+COUNTA(Config!$F$5:$F$20)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$J$5,0,0,MAX(1,COUNTA(Config!$J$5:$J$34)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="H5:H604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -21815,10 +21795,10 @@
     <dataValidation sqref="I5:I604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="G5:G604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/09-caixa-do-escritorio.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/09-caixa-do-escritorio.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
